--- a/tests/eindhoven-500/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaalproduct_Auto_OV_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaalproduct_Auto_OV_Fiets.xlsx
@@ -388,13 +388,13 @@
         <v>2920574.314209194</v>
       </c>
       <c r="C2">
-        <v>3853640.532441906</v>
+        <v>3853673.438125565</v>
       </c>
       <c r="D2">
-        <v>5981222.514400337</v>
+        <v>5984717.654988584</v>
       </c>
       <c r="E2">
-        <v>7531281.417480712</v>
+        <v>7550861.7856267</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -405,13 +405,13 @@
         <v>1214293.704169339</v>
       </c>
       <c r="C3">
-        <v>1613868.745149921</v>
+        <v>1614060.238644798</v>
       </c>
       <c r="D3">
-        <v>2503979.233498171</v>
+        <v>2505593.19391833</v>
       </c>
       <c r="E3">
-        <v>3230585.075251777</v>
+        <v>3239817.429670983</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -422,13 +422,13 @@
         <v>215438.1857389292</v>
       </c>
       <c r="C4">
-        <v>359006.4350101666</v>
+        <v>359019.5991253871</v>
       </c>
       <c r="D4">
-        <v>717863.7378731898</v>
+        <v>718248.9445645445</v>
       </c>
       <c r="E4">
-        <v>1199505.96337916</v>
+        <v>1202166.622734288</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -439,13 +439,13 @@
         <v>301613.4600345009</v>
       </c>
       <c r="C5">
-        <v>403882.2393864375</v>
+        <v>403897.0490160605</v>
       </c>
       <c r="D5">
-        <v>675636.4591747669</v>
+        <v>675999.006648983</v>
       </c>
       <c r="E5">
-        <v>820714.6065225831</v>
+        <v>822535.057660302</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -456,13 +456,13 @@
         <v>315976.0057504295</v>
       </c>
       <c r="C6">
-        <v>403882.2393864375</v>
+        <v>403897.0490160605</v>
       </c>
       <c r="D6">
-        <v>675636.4591747669</v>
+        <v>675999.006648983</v>
       </c>
       <c r="E6">
-        <v>757582.7137131536</v>
+        <v>759263.1301479711</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -473,13 +473,13 @@
         <v>1192151.651162758</v>
       </c>
       <c r="C7">
-        <v>1572051.530840323</v>
+        <v>1572302.229080056</v>
       </c>
       <c r="D7">
-        <v>2438588.328624257</v>
+        <v>2440384.850457363</v>
       </c>
       <c r="E7">
-        <v>3149174.823020254</v>
+        <v>3158832.913486288</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -490,13 +490,13 @@
         <v>999303.5899452528</v>
       </c>
       <c r="C8">
-        <v>1493448.954298307</v>
+        <v>1493687.117626053</v>
       </c>
       <c r="D8">
-        <v>2576621.630244498</v>
+        <v>2578519.841992685</v>
       </c>
       <c r="E8">
-        <v>3685204.580130085</v>
+        <v>3696506.600888209</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -507,13 +507,13 @@
         <v>981190.8925484471</v>
       </c>
       <c r="C9">
-        <v>1454978.400316995</v>
+        <v>1455260.429494224</v>
       </c>
       <c r="D9">
-        <v>2508392.249264547</v>
+        <v>2510463.367661748</v>
       </c>
       <c r="E9">
-        <v>3589199.395098731</v>
+        <v>3600923.17535923</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -524,13 +524,13 @@
         <v>911645.3803009323</v>
       </c>
       <c r="C10">
-        <v>1414846.377756291</v>
+        <v>1415072.00617205</v>
       </c>
       <c r="D10">
-        <v>2622632.730784579</v>
+        <v>2624564.839171126</v>
       </c>
       <c r="E10">
-        <v>4154230.617601187</v>
+        <v>4166971.077364891</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -541,13 +541,13 @@
         <v>999303.5899452528</v>
       </c>
       <c r="C11">
-        <v>1493448.954298307</v>
+        <v>1493687.117626053</v>
       </c>
       <c r="D11">
-        <v>2576621.630244498</v>
+        <v>2578519.841992685</v>
       </c>
       <c r="E11">
-        <v>3685204.580130085</v>
+        <v>3696506.600888209</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -558,13 +558,13 @@
         <v>215438.1857389292</v>
       </c>
       <c r="C12">
-        <v>359006.4350101666</v>
+        <v>359019.5991253871</v>
       </c>
       <c r="D12">
-        <v>717863.7378731898</v>
+        <v>718248.9445645445</v>
       </c>
       <c r="E12">
-        <v>1199505.96337916</v>
+        <v>1202166.622734288</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -575,13 +575,13 @@
         <v>928577.5384824359</v>
       </c>
       <c r="C13">
-        <v>1452481.870634929</v>
+        <v>1452654.214780318</v>
       </c>
       <c r="D13">
-        <v>2692958.798290486</v>
+        <v>2694694.567044241</v>
       </c>
       <c r="E13">
-        <v>4261622.865225749</v>
+        <v>4273801.71573619</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -592,13 +592,13 @@
         <v>215438.1857389292</v>
       </c>
       <c r="C14">
-        <v>359006.4350101666</v>
+        <v>359019.5991253871</v>
       </c>
       <c r="D14">
-        <v>717863.7378731898</v>
+        <v>718248.9445645445</v>
       </c>
       <c r="E14">
-        <v>1199505.96337916</v>
+        <v>1202166.622734288</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -609,13 +609,13 @@
         <v>999303.5899452528</v>
       </c>
       <c r="C15">
-        <v>1493448.954298307</v>
+        <v>1493687.117626053</v>
       </c>
       <c r="D15">
-        <v>2576621.630244498</v>
+        <v>2578519.841992685</v>
       </c>
       <c r="E15">
-        <v>3685204.580130085</v>
+        <v>3696506.600888209</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -626,13 +626,13 @@
         <v>2415388.73251795</v>
       </c>
       <c r="C16">
-        <v>3596327.42899786</v>
+        <v>3596379.252830145</v>
       </c>
       <c r="D16">
-        <v>6128105.855856314</v>
+        <v>6132165.865583995</v>
       </c>
       <c r="E16">
-        <v>8679199.169827299</v>
+        <v>8703126.326372812</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -643,13 +643,13 @@
         <v>215438.1857389292</v>
       </c>
       <c r="C17">
-        <v>359006.4350101666</v>
+        <v>359019.5991253871</v>
       </c>
       <c r="D17">
-        <v>717863.7378731898</v>
+        <v>718248.9445645445</v>
       </c>
       <c r="E17">
-        <v>1199505.96337916</v>
+        <v>1202166.622734288</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -660,13 +660,13 @@
         <v>1017863.840259593</v>
       </c>
       <c r="C18">
-        <v>1533175.307892425</v>
+        <v>1533357.226712558</v>
       </c>
       <c r="D18">
-        <v>2645713.907092408</v>
+        <v>2647419.223762764</v>
       </c>
       <c r="E18">
-        <v>3780471.896571229</v>
+        <v>3791275.715572426</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -677,13 +677,13 @@
         <v>2415388.73251795</v>
       </c>
       <c r="C19">
-        <v>3596327.42899786</v>
+        <v>3596379.252830145</v>
       </c>
       <c r="D19">
-        <v>6128105.855856314</v>
+        <v>6132165.865583995</v>
       </c>
       <c r="E19">
-        <v>8679199.169827299</v>
+        <v>8703126.326372812</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -694,13 +694,13 @@
         <v>2415388.73251795</v>
       </c>
       <c r="C20">
-        <v>3596327.42899786</v>
+        <v>3596379.252830145</v>
       </c>
       <c r="D20">
-        <v>6128105.855856314</v>
+        <v>6132165.865583995</v>
       </c>
       <c r="E20">
-        <v>8679199.169827299</v>
+        <v>8703126.326372812</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -711,13 +711,13 @@
         <v>2415388.73251795</v>
       </c>
       <c r="C21">
-        <v>3596327.42899786</v>
+        <v>3596379.252830145</v>
       </c>
       <c r="D21">
-        <v>6128105.855856314</v>
+        <v>6132165.865583995</v>
       </c>
       <c r="E21">
-        <v>8679199.169827299</v>
+        <v>8703126.326372812</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -725,16 +725,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>566984.2496974241</v>
+        <v>566985.1873986969</v>
       </c>
       <c r="C22">
-        <v>753458.5281593553</v>
+        <v>755424.8183328288</v>
       </c>
       <c r="D22">
-        <v>1115308.876446426</v>
+        <v>1120445.390787933</v>
       </c>
       <c r="E22">
-        <v>1427948.12942514</v>
+        <v>1436842.983711747</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -745,13 +745,13 @@
         <v>2463134.963790887</v>
       </c>
       <c r="C23">
-        <v>3696349.082138155</v>
+        <v>3696380.644732685</v>
       </c>
       <c r="D23">
-        <v>6300829.824330126</v>
+        <v>6304511.728155913</v>
       </c>
       <c r="E23">
-        <v>8918622.73122716</v>
+        <v>8941810.009294776</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -762,13 +762,13 @@
         <v>1459814.217494129</v>
       </c>
       <c r="C24">
-        <v>2108613.301768977</v>
+        <v>2108772.254940837</v>
       </c>
       <c r="D24">
-        <v>3876152.132841001</v>
+        <v>3878962.953044999</v>
       </c>
       <c r="E24">
-        <v>5065059.868328501</v>
+        <v>5072014.474387075</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -779,13 +779,13 @@
         <v>1718646.525560464</v>
       </c>
       <c r="C25">
-        <v>2242493.511405103</v>
+        <v>2242662.556841842</v>
       </c>
       <c r="D25">
-        <v>3666630.395930676</v>
+        <v>3669289.279907432</v>
       </c>
       <c r="E25">
-        <v>3892098.635662953</v>
+        <v>3897442.701371121</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -796,13 +796,13 @@
         <v>1718646.525560464</v>
       </c>
       <c r="C26">
-        <v>2242493.511405103</v>
+        <v>2242662.556841842</v>
       </c>
       <c r="D26">
-        <v>3666630.395930676</v>
+        <v>3669289.279907432</v>
       </c>
       <c r="E26">
-        <v>3892098.635662953</v>
+        <v>3897442.701371121</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -813,13 +813,13 @@
         <v>961154.3453853888</v>
       </c>
       <c r="C27">
-        <v>1309587.279960375</v>
+        <v>1309598.133659202</v>
       </c>
       <c r="D27">
-        <v>2223306.103155304</v>
+        <v>2227150.168454812</v>
       </c>
       <c r="E27">
-        <v>3150599.124766477</v>
+        <v>3159360.633815194</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -830,13 +830,13 @@
         <v>1167115.990825115</v>
       </c>
       <c r="C28">
-        <v>1408424.055806441</v>
+        <v>1408435.72865235</v>
       </c>
       <c r="D28">
-        <v>2092523.391204992</v>
+        <v>2096141.335016294</v>
       </c>
       <c r="E28">
-        <v>2443321.770227063</v>
+        <v>2450116.409897498</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -847,13 +847,13 @@
         <v>1167115.990825115</v>
       </c>
       <c r="C29">
-        <v>1408424.055806441</v>
+        <v>1408435.72865235</v>
       </c>
       <c r="D29">
-        <v>2092523.391204992</v>
+        <v>2096141.335016294</v>
       </c>
       <c r="E29">
-        <v>2443321.770227063</v>
+        <v>2450116.409897498</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -864,13 +864,13 @@
         <v>5014938.581559462</v>
       </c>
       <c r="C30">
-        <v>6709144.18615722</v>
+        <v>6723856.759756933</v>
       </c>
       <c r="D30">
-        <v>10061564.58714304</v>
+        <v>10120298.85951555</v>
       </c>
       <c r="E30">
-        <v>13439690.16190087</v>
+        <v>13502482.33460237</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -881,13 +881,13 @@
         <v>4265579.942935633</v>
       </c>
       <c r="C31">
-        <v>6119329.312648893</v>
+        <v>6132748.473184895</v>
       </c>
       <c r="D31">
-        <v>10400718.44963101</v>
+        <v>10461432.52893743</v>
       </c>
       <c r="E31">
-        <v>15876125.22049109</v>
+        <v>15950300.76953029</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -898,13 +898,13 @@
         <v>3332476.073718317</v>
       </c>
       <c r="C32">
-        <v>5424489.24101026</v>
+        <v>5436092.920437198</v>
       </c>
       <c r="D32">
-        <v>10968814.75165984</v>
+        <v>11029143.03272275</v>
       </c>
       <c r="E32">
-        <v>19590015.26996119</v>
+        <v>19676105.96309112</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -915,13 +915,13 @@
         <v>4640259.262247548</v>
       </c>
       <c r="C33">
-        <v>6377373.319808787</v>
+        <v>6391358.348560162</v>
       </c>
       <c r="D33">
-        <v>10174615.87463903</v>
+        <v>10234010.08265618</v>
       </c>
       <c r="E33">
-        <v>14697205.03085066</v>
+        <v>14765872.49456517</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -929,16 +929,16 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>2989800.678375401</v>
+        <v>2991112.760611125</v>
       </c>
       <c r="C34">
-        <v>4722488.914461209</v>
+        <v>4739024.529917625</v>
       </c>
       <c r="D34">
-        <v>8421034.497427467</v>
+        <v>8466858.002476169</v>
       </c>
       <c r="E34">
-        <v>13682601.81876187</v>
+        <v>13724865.08362418</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -949,13 +949,13 @@
         <v>17097358.48667554</v>
       </c>
       <c r="C35">
-        <v>23138332.29943681</v>
+        <v>23175227.78023947</v>
       </c>
       <c r="D35">
-        <v>38400857.64683268</v>
+        <v>38623635.84161607</v>
       </c>
       <c r="E35">
-        <v>59342854.82613456</v>
+        <v>59522396.4076703</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -966,13 +966,13 @@
         <v>3208495.98254055</v>
       </c>
       <c r="C36">
-        <v>4825730.275640732</v>
+        <v>4831773.300215753</v>
       </c>
       <c r="D36">
-        <v>8242049.069928823</v>
+        <v>8269042.311599573</v>
       </c>
       <c r="E36">
-        <v>12307436.95356586</v>
+        <v>12347991.02462929</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -983,13 +983,13 @@
         <v>3396919.65563528</v>
       </c>
       <c r="C37">
-        <v>4325122.779553515</v>
+        <v>4333379.638570908</v>
       </c>
       <c r="D37">
-        <v>6208817.976432353</v>
+        <v>6253912.321714579</v>
       </c>
       <c r="E37">
-        <v>8121227.226414364</v>
+        <v>8160663.353966905</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1000,13 +1000,13 @@
         <v>2333536.111262497</v>
       </c>
       <c r="C38">
-        <v>3460098.223642812</v>
+        <v>3466703.710856726</v>
       </c>
       <c r="D38">
-        <v>6664511.038922802</v>
+        <v>6712915.060922989</v>
       </c>
       <c r="E38">
-        <v>11511642.47627667</v>
+        <v>11567542.22989484</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1014,16 +1014,16 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>4864657.184517113</v>
+        <v>4866819.138200978</v>
       </c>
       <c r="C39">
-        <v>5587576.828325586</v>
+        <v>5607534.790262774</v>
       </c>
       <c r="D39">
-        <v>7411784.256374499</v>
+        <v>7455141.679006455</v>
       </c>
       <c r="E39">
-        <v>8847359.145675112</v>
+        <v>8877641.041673407</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1034,13 +1034,13 @@
         <v>22244192.17544797</v>
       </c>
       <c r="C40">
-        <v>25883558.16547168</v>
+        <v>25924831.07620008</v>
       </c>
       <c r="D40">
-        <v>36249903.51175474</v>
+        <v>36460203.19150908</v>
       </c>
       <c r="E40">
-        <v>47015184.41096334</v>
+        <v>47157428.67255254</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1051,13 +1051,13 @@
         <v>26509718.72573198</v>
       </c>
       <c r="C41">
-        <v>27147233.56412266</v>
+        <v>27190521.48227719</v>
       </c>
       <c r="D41">
-        <v>34288739.44741897</v>
+        <v>34487661.657588</v>
       </c>
       <c r="E41">
-        <v>39108471.66192248</v>
+        <v>39226794.19416668</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1068,13 +1068,13 @@
         <v>2157306.95448576</v>
       </c>
       <c r="C42">
-        <v>3527042.795735501</v>
+        <v>3532087.094660821</v>
       </c>
       <c r="D42">
-        <v>6732800.54530595</v>
+        <v>6782475.066165396</v>
       </c>
       <c r="E42">
-        <v>11367237.73421564</v>
+        <v>11429663.34896085</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1085,13 +1085,13 @@
         <v>2517366.974563682</v>
       </c>
       <c r="C43">
-        <v>3753395.64127436</v>
+        <v>3758617.866099522</v>
       </c>
       <c r="D43">
-        <v>6714399.451546606</v>
+        <v>6760814.030661202</v>
       </c>
       <c r="E43">
-        <v>10778577.27641007</v>
+        <v>10833002.07277648</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1102,13 +1102,13 @@
         <v>8244143.598319246</v>
       </c>
       <c r="C44">
-        <v>10014263.14759973</v>
+        <v>10045938.50702259</v>
       </c>
       <c r="D44">
-        <v>14448695.76476914</v>
+        <v>14565592.50505563</v>
       </c>
       <c r="E44">
-        <v>17551410.19039119</v>
+        <v>17661784.78020799</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1119,13 +1119,13 @@
         <v>1236331.998044455</v>
       </c>
       <c r="C45">
-        <v>1805651.259922227</v>
+        <v>1806372.237304905</v>
       </c>
       <c r="D45">
-        <v>3209990.458571625</v>
+        <v>3224382.72357805</v>
       </c>
       <c r="E45">
-        <v>4894592.138981006</v>
+        <v>4913587.140924104</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1136,13 +1136,13 @@
         <v>2668026.771017737</v>
       </c>
       <c r="C46">
-        <v>3919320.879959431</v>
+        <v>3926626.432986377</v>
       </c>
       <c r="D46">
-        <v>6746151.089665909</v>
+        <v>6792373.888596627</v>
       </c>
       <c r="E46">
-        <v>10506882.31829913</v>
+        <v>10553988.69968668</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1153,13 +1153,13 @@
         <v>4550099.372000555</v>
       </c>
       <c r="C47">
-        <v>5375145.670262119</v>
+        <v>5381695.65585718</v>
       </c>
       <c r="D47">
-        <v>7716258.050738689</v>
+        <v>7740079.171482766</v>
       </c>
       <c r="E47">
-        <v>9419866.693066262</v>
+        <v>9449009.858918017</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1170,13 +1170,13 @@
         <v>1749041.42135667</v>
       </c>
       <c r="C48">
-        <v>2114292.558180517</v>
+        <v>2115109.043422528</v>
       </c>
       <c r="D48">
-        <v>3015724.667940672</v>
+        <v>3028502.962305344</v>
       </c>
       <c r="E48">
-        <v>3683531.213993355</v>
+        <v>3696830.287902765</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1187,13 +1187,13 @@
         <v>15570625.49352532</v>
       </c>
       <c r="C49">
-        <v>23339402.60449305</v>
+        <v>23356814.54253545</v>
       </c>
       <c r="D49">
-        <v>36252089.08087488</v>
+        <v>36313027.55098671</v>
       </c>
       <c r="E49">
-        <v>49139086.38816888</v>
+        <v>49170761.73054086</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1207,10 +1207,10 @@
         <v>7434556.688147866</v>
       </c>
       <c r="D50">
-        <v>13607825.30080598</v>
+        <v>13610079.45169501</v>
       </c>
       <c r="E50">
-        <v>22243693.30807471</v>
+        <v>22247746.96503334</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1221,13 +1221,13 @@
         <v>2091702.298900684</v>
       </c>
       <c r="C51">
-        <v>3004447.037742368</v>
+        <v>3006261.887425763</v>
       </c>
       <c r="D51">
-        <v>4809546.824599941</v>
+        <v>4820711.742468589</v>
       </c>
       <c r="E51">
-        <v>6293297.234984625</v>
+        <v>6301479.450897912</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1238,13 +1238,13 @@
         <v>1857210.334583838</v>
       </c>
       <c r="C52">
-        <v>2841220.524040801</v>
+        <v>2848786.065022514</v>
       </c>
       <c r="D52">
-        <v>4834192.482819824</v>
+        <v>4847569.487673499</v>
       </c>
       <c r="E52">
-        <v>6865650.42908169</v>
+        <v>6878548.777724721</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1255,13 +1255,13 @@
         <v>1898856.424611885</v>
       </c>
       <c r="C53">
-        <v>3011741.149334182</v>
+        <v>3012637.587252665</v>
       </c>
       <c r="D53">
-        <v>5478359.809232601</v>
+        <v>5488875.467302154</v>
       </c>
       <c r="E53">
-        <v>8306842.730193443</v>
+        <v>8313067.587284455</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1272,13 +1272,13 @@
         <v>1605636.484504493</v>
       </c>
       <c r="C54">
-        <v>2541963.091481545</v>
+        <v>2543560.689335169</v>
       </c>
       <c r="D54">
-        <v>4966484.97941114</v>
+        <v>4979130.648867795</v>
       </c>
       <c r="E54">
-        <v>7954386.682238982</v>
+        <v>7965724.640115149</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1292,10 +1292,10 @@
         <v>9195372.745867098</v>
       </c>
       <c r="D55">
-        <v>12359005.89028897</v>
+        <v>12361053.17290021</v>
       </c>
       <c r="E55">
-        <v>14181825.62763494</v>
+        <v>14184410.10204507</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1306,13 +1306,13 @@
         <v>6959993.210085494</v>
       </c>
       <c r="C56">
-        <v>12409259.58605038</v>
+        <v>12431492.7330156</v>
       </c>
       <c r="D56">
-        <v>21579560.25854418</v>
+        <v>21622320.77797912</v>
       </c>
       <c r="E56">
-        <v>32841493.43394931</v>
+        <v>32914710.00951288</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1323,13 +1323,13 @@
         <v>5352090.927884393</v>
       </c>
       <c r="C57">
-        <v>8731020.223210987</v>
+        <v>8735226.870638784</v>
       </c>
       <c r="D57">
-        <v>17648847.84627605</v>
+        <v>17684919.34129187</v>
       </c>
       <c r="E57">
-        <v>29224005.56242708</v>
+        <v>29256449.66361968</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1343,10 +1343,10 @@
         <v>1355467.642345738</v>
       </c>
       <c r="D58">
-        <v>2195796.312155455</v>
+        <v>2196981.872028033</v>
       </c>
       <c r="E58">
-        <v>3149372.127949656</v>
+        <v>3155116.139832374</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1360,10 +1360,10 @@
         <v>1355467.642345738</v>
       </c>
       <c r="D59">
-        <v>2195796.312155455</v>
+        <v>2196981.872028033</v>
       </c>
       <c r="E59">
-        <v>3149372.127949656</v>
+        <v>3155116.139832374</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1374,13 +1374,13 @@
         <v>2134227.820695361</v>
       </c>
       <c r="C60">
-        <v>2944658.420556566</v>
+        <v>2944662.439501397</v>
       </c>
       <c r="D60">
-        <v>5228552.5733338</v>
+        <v>5232238.125616066</v>
       </c>
       <c r="E60">
-        <v>7089262.640608231</v>
+        <v>7094940.615854421</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1391,13 +1391,13 @@
         <v>2459001.619496829</v>
       </c>
       <c r="C61">
-        <v>3084050.535139125</v>
+        <v>3084054.744329866</v>
       </c>
       <c r="D61">
-        <v>4990891.092727718</v>
+        <v>4994409.119906245</v>
       </c>
       <c r="E61">
-        <v>5916219.182090322</v>
+        <v>5920957.63625261</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1408,13 +1408,13 @@
         <v>346247.5559102879</v>
       </c>
       <c r="C62">
-        <v>624559.5412053384</v>
+        <v>624576.5718976485</v>
       </c>
       <c r="D62">
-        <v>1633772.575685403</v>
+        <v>1634542.181483475</v>
       </c>
       <c r="E62">
-        <v>2636296.160805245</v>
+        <v>2638392.410803792</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1425,13 +1425,13 @@
         <v>427038.6522893552</v>
       </c>
       <c r="C63">
-        <v>689169.1489162355</v>
+        <v>689187.9414043018</v>
       </c>
       <c r="D63">
-        <v>1519121.868619761</v>
+        <v>1519837.466993406</v>
       </c>
       <c r="E63">
-        <v>1977222.120603934</v>
+        <v>1978794.308102844</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1442,13 +1442,13 @@
         <v>433702.6279263441</v>
       </c>
       <c r="C64">
-        <v>777193.0565200197</v>
+        <v>777452.0207760889</v>
       </c>
       <c r="D64">
-        <v>1925690.069012019</v>
+        <v>1926479.343890644</v>
       </c>
       <c r="E64">
-        <v>2510615.360173576</v>
+        <v>2512289.945255752</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1459,13 +1459,13 @@
         <v>400340.8873166253</v>
       </c>
       <c r="C65">
-        <v>759326.5494735824</v>
+        <v>759579.5605283628</v>
       </c>
       <c r="D65">
-        <v>1952069.385025882</v>
+        <v>1952869.471889146</v>
       </c>
       <c r="E65">
-        <v>2774890.661244479</v>
+        <v>2776741.518440567</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1476,13 +1476,13 @@
         <v>1510454.308784737</v>
       </c>
       <c r="C66">
-        <v>2307348.347134846</v>
+        <v>2308482.937709365</v>
       </c>
       <c r="D66">
-        <v>4162953.454541825</v>
+        <v>4170644.26257063</v>
       </c>
       <c r="E66">
-        <v>6230250.876518453</v>
+        <v>6251637.615738894</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1493,13 +1493,13 @@
         <v>985802.2711308396</v>
       </c>
       <c r="C67">
-        <v>1855796.290749557</v>
+        <v>1856640.545058458</v>
       </c>
       <c r="D67">
-        <v>4573521.295879926</v>
+        <v>4581320.335644893</v>
       </c>
       <c r="E67">
-        <v>9054580.027195273</v>
+        <v>9083974.312031565</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -1510,13 +1510,13 @@
         <v>1219982.326326134</v>
       </c>
       <c r="C68">
-        <v>2001555.192695288</v>
+        <v>2002539.415844268</v>
       </c>
       <c r="D68">
-        <v>4311630.363632604</v>
+        <v>4319595.843376724</v>
       </c>
       <c r="E68">
-        <v>7769489.328364188</v>
+        <v>7796159.850215562</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1527,13 +1527,13 @@
         <v>1419555.270428409</v>
       </c>
       <c r="C69">
-        <v>2198404.83673409</v>
+        <v>2199404.953376943</v>
       </c>
       <c r="D69">
-        <v>4319436.779442152</v>
+        <v>4326802.539220177</v>
       </c>
       <c r="E69">
-        <v>7183799.029840878</v>
+        <v>7207120.115330828</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -1544,13 +1544,13 @@
         <v>1123814.589089157</v>
       </c>
       <c r="C70">
-        <v>2027100.563741824</v>
+        <v>2028022.7492177</v>
       </c>
       <c r="D70">
-        <v>4522704.392592371</v>
+        <v>4530416.77635995</v>
       </c>
       <c r="E70">
-        <v>8156605.148465164</v>
+        <v>8183084.297615211</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -1561,13 +1561,13 @@
         <v>6033900.234537147</v>
       </c>
       <c r="C71">
-        <v>7822171.259234969</v>
+        <v>7825131.388199765</v>
       </c>
       <c r="D71">
-        <v>12711275.84093338</v>
+        <v>12734984.68725092</v>
       </c>
       <c r="E71">
-        <v>17261074.24535955</v>
+        <v>17314937.04859613</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1578,13 +1578,13 @@
         <v>1735011.997190278</v>
       </c>
       <c r="C72">
-        <v>2455361.24622249</v>
+        <v>2456478.259615806</v>
       </c>
       <c r="D72">
-        <v>4166986.069579488</v>
+        <v>4174091.861365347</v>
       </c>
       <c r="E72">
-        <v>5762005.471851538</v>
+        <v>5780710.925838268</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1595,13 +1595,13 @@
         <v>1813876.178880745</v>
       </c>
       <c r="C73">
-        <v>2426810.534057113</v>
+        <v>2427914.558922599</v>
       </c>
       <c r="D73">
-        <v>4116169.166291933</v>
+        <v>4123188.302080404</v>
       </c>
       <c r="E73">
-        <v>5612342.992063186</v>
+        <v>5630562.59010221</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1612,13 +1612,13 @@
         <v>1892740.360571212</v>
       </c>
       <c r="C74">
-        <v>2598114.80704938</v>
+        <v>2599296.763081841</v>
       </c>
       <c r="D74">
-        <v>4065352.263004378</v>
+        <v>4072284.742795461</v>
       </c>
       <c r="E74">
-        <v>5013693.07290978</v>
+        <v>5029969.247157973</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1629,13 +1629,13 @@
         <v>1974392.084801737</v>
       </c>
       <c r="C75">
-        <v>2570768.999157273</v>
+        <v>2570871.706390029</v>
       </c>
       <c r="D75">
-        <v>4129275.492601795</v>
+        <v>4132897.06413822</v>
       </c>
       <c r="E75">
-        <v>4681147.756373056</v>
+        <v>4696291.49758252</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1646,13 +1646,13 @@
         <v>1537851.54296411</v>
       </c>
       <c r="C76">
-        <v>2369709.109726357</v>
+        <v>2370787.157536185</v>
       </c>
       <c r="D76">
-        <v>4268619.876154597</v>
+        <v>4275898.979935233</v>
       </c>
       <c r="E76">
-        <v>6360655.391004944</v>
+        <v>6381304.268782504</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -1663,13 +1663,13 @@
         <v>3625818.588231245</v>
       </c>
       <c r="C77">
-        <v>5132405.675980504</v>
+        <v>5132860.257544571</v>
       </c>
       <c r="D77">
-        <v>9063641.210381702</v>
+        <v>9076924.204993013</v>
       </c>
       <c r="E77">
-        <v>13124167.13852421</v>
+        <v>13164263.10884582</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1680,13 +1680,13 @@
         <v>2410982.463308405</v>
       </c>
       <c r="C78">
-        <v>4859405.374066647</v>
+        <v>4859835.775760285</v>
       </c>
       <c r="D78">
-        <v>9960045.286133738</v>
+        <v>9974641.983508807</v>
       </c>
       <c r="E78">
-        <v>16312524.12697925</v>
+        <v>16362360.92624905</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1697,13 +1697,13 @@
         <v>4485548.768945869</v>
       </c>
       <c r="C79">
-        <v>5432706.008085746</v>
+        <v>5433187.187507285</v>
       </c>
       <c r="D79">
-        <v>8466038.493213678</v>
+        <v>8478445.685982484</v>
       </c>
       <c r="E79">
-        <v>10454845.00865488</v>
+        <v>10486785.86636871</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1714,13 +1714,13 @@
         <v>4223891.757424027</v>
       </c>
       <c r="C80">
-        <v>5296205.857128819</v>
+        <v>5296674.946615142</v>
       </c>
       <c r="D80">
-        <v>8665239.398936352</v>
+        <v>8677938.525652662</v>
       </c>
       <c r="E80">
-        <v>11270471.21500384</v>
+        <v>11304903.91268116</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1731,13 +1731,13 @@
         <v>953409.7747756895</v>
       </c>
       <c r="C81">
-        <v>1214981.092299888</v>
+        <v>1215217.587552961</v>
       </c>
       <c r="D81">
-        <v>1940268.147119438</v>
+        <v>1943998.390192817</v>
       </c>
       <c r="E81">
-        <v>2763761.843587961</v>
+        <v>2769963.303368331</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1748,13 +1748,13 @@
         <v>1065575.630631653</v>
       </c>
       <c r="C82">
-        <v>1362251.527730178</v>
+        <v>1362516.689074532</v>
       </c>
       <c r="D82">
-        <v>1883201.436910043</v>
+        <v>1886821.966951852</v>
       </c>
       <c r="E82">
-        <v>2211009.474870368</v>
+        <v>2215970.642694665</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -1765,13 +1765,13 @@
         <v>2176112.834713697</v>
       </c>
       <c r="C83">
-        <v>3648346.793771369</v>
+        <v>3648383.271013031</v>
       </c>
       <c r="D83">
-        <v>7638722.348389461</v>
+        <v>7657207.304607979</v>
       </c>
       <c r="E83">
-        <v>13025204.93660032</v>
+        <v>13082003.88122088</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -1782,13 +1782,13 @@
         <v>3735374.787146347</v>
       </c>
       <c r="C84">
-        <v>4445667.616251204</v>
+        <v>4445712.065340383</v>
       </c>
       <c r="D84">
-        <v>6667324.130675194</v>
+        <v>6683458.398819681</v>
       </c>
       <c r="E84">
-        <v>7509429.376713452</v>
+        <v>7542175.707030403</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -1799,13 +1799,13 @@
         <v>2451757.332276883</v>
       </c>
       <c r="C85">
-        <v>2845641.462519525</v>
+        <v>2846153.876123528</v>
       </c>
       <c r="D85">
-        <v>4056914.37263688</v>
+        <v>4092994.736332469</v>
       </c>
       <c r="E85">
-        <v>4876722.510068703</v>
+        <v>4908311.387567285</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -1816,13 +1816,13 @@
         <v>2505642.108810441</v>
       </c>
       <c r="C86">
-        <v>2952353.017364007</v>
+        <v>2952884.64647816</v>
       </c>
       <c r="D86">
-        <v>4001340.203148704</v>
+        <v>4036926.315286818</v>
       </c>
       <c r="E86">
-        <v>4567089.334826245</v>
+        <v>4596672.569309046</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -1833,13 +1833,13 @@
         <v>748369.1259892735</v>
       </c>
       <c r="C87">
-        <v>1014313.692866396</v>
+        <v>1016875.04426676</v>
       </c>
       <c r="D87">
-        <v>1575423.603306354</v>
+        <v>1592005.313547462</v>
       </c>
       <c r="E87">
-        <v>2280543.930755072</v>
+        <v>2296488.152794485</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -1850,13 +1850,13 @@
         <v>696757.4621279443</v>
       </c>
       <c r="C88">
-        <v>979337.3586296237</v>
+        <v>981810.3875679061</v>
       </c>
       <c r="D88">
-        <v>1631688.731995867</v>
+        <v>1648862.646174158</v>
       </c>
       <c r="E88">
-        <v>2437822.822531284</v>
+        <v>2454866.646090657</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -1867,13 +1867,13 @@
         <v>799980.7898506027</v>
       </c>
       <c r="C89">
-        <v>1049290.027103168</v>
+        <v>1051939.700965614</v>
       </c>
       <c r="D89">
-        <v>1575423.603306354</v>
+        <v>1592005.313547462</v>
       </c>
       <c r="E89">
-        <v>2044625.593090754</v>
+        <v>2058920.412850229</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -1881,16 +1881,16 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>163617863.9379515</v>
+        <v>163618833.0995198</v>
       </c>
       <c r="C90">
-        <v>196082472.2183633</v>
+        <v>196123209.8506031</v>
       </c>
       <c r="D90">
-        <v>241127179.2878412</v>
+        <v>241282635.260735</v>
       </c>
       <c r="E90">
-        <v>287805448.4474276</v>
+        <v>287934157.8107107</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -1898,16 +1898,16 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>37745121.38480134</v>
+        <v>37745344.96137271</v>
       </c>
       <c r="C91">
-        <v>50280829.19234308</v>
+        <v>50291275.41889856</v>
       </c>
       <c r="D91">
-        <v>66918682.98151163</v>
+        <v>66961825.81177402</v>
       </c>
       <c r="E91">
-        <v>86332157.89779602</v>
+        <v>86370766.46873806</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -1915,16 +1915,16 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>33681118.6398301</v>
+        <v>33681318.14399777</v>
       </c>
       <c r="C92">
-        <v>47473270.20190768</v>
+        <v>47483133.13662504</v>
       </c>
       <c r="D92">
-        <v>69353517.69093283</v>
+        <v>69398230.27206157</v>
       </c>
       <c r="E92">
-        <v>98272719.80243082</v>
+        <v>98316668.30744387</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -1932,16 +1932,16 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>67974621.25492984</v>
+        <v>67975023.89061369</v>
       </c>
       <c r="C93">
-        <v>90416161.1237946</v>
+        <v>90434945.77230869</v>
       </c>
       <c r="D93">
-        <v>129988756.2610349</v>
+        <v>130072560.7024483</v>
       </c>
       <c r="E93">
-        <v>183088615.8710669</v>
+        <v>183170494.8601558</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -1949,16 +1949,16 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>43200079.4163406</v>
+        <v>43200120.2605272</v>
       </c>
       <c r="C94">
-        <v>71489662.22273143</v>
+        <v>71505436.82325915</v>
       </c>
       <c r="D94">
-        <v>143951176.9281095</v>
+        <v>144048961.7429084</v>
       </c>
       <c r="E94">
-        <v>255987161.334991</v>
+        <v>256107836.5619258</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -1966,16 +1966,16 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>19763301.02006559</v>
+        <v>19763418.08449456</v>
       </c>
       <c r="C95">
-        <v>26288961.45589511</v>
+        <v>26294423.18856118</v>
       </c>
       <c r="D95">
-        <v>35422917.86932129</v>
+        <v>35445755.21257052</v>
       </c>
       <c r="E95">
-        <v>46530284.8823467</v>
+        <v>46551093.67305202</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -1983,16 +1983,16 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>6068168.482217324</v>
+        <v>6068204.425943401</v>
       </c>
       <c r="C96">
-        <v>8486485.130179733</v>
+        <v>8488248.262326786</v>
       </c>
       <c r="D96">
-        <v>12645431.8779617</v>
+        <v>12653584.4550418</v>
       </c>
       <c r="E96">
-        <v>18195141.94991969</v>
+        <v>18203278.99231362</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2000,16 +2000,16 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>6346524.834612614</v>
+        <v>6346562.427133465</v>
       </c>
       <c r="C97">
-        <v>8933142.242294457</v>
+        <v>8934998.170870302</v>
       </c>
       <c r="D97">
-        <v>12802517.98824694</v>
+        <v>12810771.83957648</v>
       </c>
       <c r="E97">
-        <v>18005609.22127469</v>
+        <v>18013661.50281035</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2017,16 +2017,16 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>7202594.40334896</v>
+        <v>7202626.337915828</v>
       </c>
       <c r="C98">
-        <v>11101447.380261</v>
+        <v>11105193.18297911</v>
       </c>
       <c r="D98">
-        <v>17300786.12972582</v>
+        <v>17323225.88778928</v>
       </c>
       <c r="E98">
-        <v>25675067.19312919</v>
+        <v>25695525.9994187</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2034,16 +2034,16 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>3734678.579514275</v>
+        <v>3734695.138178577</v>
       </c>
       <c r="C99">
-        <v>4552840.779545241</v>
+        <v>4554376.979536375</v>
       </c>
       <c r="D99">
-        <v>6055275.145404036</v>
+        <v>6063129.060726248</v>
       </c>
       <c r="E99">
-        <v>7607427.316482721</v>
+        <v>7613489.18501295</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2054,13 +2054,13 @@
         <v>9623439.64921955</v>
       </c>
       <c r="C100">
-        <v>11488936.19415341</v>
+        <v>11491662.61925641</v>
       </c>
       <c r="D100">
-        <v>14933729.31903121</v>
+        <v>14950574.99450612</v>
       </c>
       <c r="E100">
-        <v>18931874.22789326</v>
+        <v>18945373.11834421</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2071,13 +2071,13 @@
         <v>4572463.037750726</v>
       </c>
       <c r="C101">
-        <v>6143816.146606103</v>
+        <v>6145274.127944604</v>
       </c>
       <c r="D101">
-        <v>8898336.122738807</v>
+        <v>8908373.701389654</v>
       </c>
       <c r="E101">
-        <v>12432872.62727318</v>
+        <v>12441737.5702559</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2088,13 +2088,13 @@
         <v>957027.1474361984</v>
       </c>
       <c r="C102">
-        <v>1105886.906389098</v>
+        <v>1106149.343030029</v>
       </c>
       <c r="D102">
-        <v>1392783.045298248</v>
+        <v>1394354.144565337</v>
       </c>
       <c r="E102">
-        <v>1695391.721900888</v>
+        <v>1696600.577762168</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2102,16 +2102,16 @@
         <v>102</v>
       </c>
       <c r="B103">
-        <v>4899479.896173147</v>
+        <v>4899485.304622944</v>
       </c>
       <c r="C103">
-        <v>6111848.24411992</v>
+        <v>6117992.943060424</v>
       </c>
       <c r="D103">
-        <v>8102791.335906722</v>
+        <v>8120818.763331911</v>
       </c>
       <c r="E103">
-        <v>9975562.812495433</v>
+        <v>9986240.484806174</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2119,16 +2119,16 @@
         <v>103</v>
       </c>
       <c r="B104">
-        <v>11516303.26110802</v>
+        <v>11516315.9737529</v>
       </c>
       <c r="C104">
-        <v>15099860.36782568</v>
+        <v>15115041.38873752</v>
       </c>
       <c r="D104">
-        <v>20990088.03206313</v>
+        <v>21036787.65358362</v>
       </c>
       <c r="E104">
-        <v>27668070.44220432</v>
+        <v>27697685.87295298</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2139,13 +2139,13 @@
         <v>1220017.492889053</v>
       </c>
       <c r="C105">
-        <v>1976888.370807248</v>
+        <v>1976935.041117476</v>
       </c>
       <c r="D105">
-        <v>2935617.436188855</v>
+        <v>2938517.436266287</v>
       </c>
       <c r="E105">
-        <v>3966050.490961207</v>
+        <v>3969276.363043625</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2153,16 +2153,16 @@
         <v>105</v>
       </c>
       <c r="B106">
-        <v>1291821.266047005</v>
+        <v>1291822.659977365</v>
       </c>
       <c r="C106">
-        <v>1921870.88988873</v>
+        <v>1923669.325882653</v>
       </c>
       <c r="D106">
-        <v>3021564.023156379</v>
+        <v>3027496.722216928</v>
       </c>
       <c r="E106">
-        <v>4222131.71270606</v>
+        <v>4225837.798363623</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2170,16 +2170,16 @@
         <v>106</v>
       </c>
       <c r="B107">
-        <v>5580667.869323062</v>
+        <v>5580673.891102215</v>
       </c>
       <c r="C107">
-        <v>8369437.74628963</v>
+        <v>8377269.644972843</v>
       </c>
       <c r="D107">
-        <v>14153642.0032062</v>
+        <v>14181432.01459509</v>
       </c>
       <c r="E107">
-        <v>22262149.03063196</v>
+        <v>22281690.20955365</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2190,13 +2190,13 @@
         <v>11739233.80629939</v>
       </c>
       <c r="C108">
-        <v>15174206.42443824</v>
+        <v>15174512.27649324</v>
       </c>
       <c r="D108">
-        <v>21005599.95366471</v>
+        <v>21024055.25021757</v>
       </c>
       <c r="E108">
-        <v>27426293.20830972</v>
+        <v>27444113.72851134</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2207,13 +2207,13 @@
         <v>1754251.319907909</v>
       </c>
       <c r="C109">
-        <v>2555258.740559264</v>
+        <v>2558477.642063477</v>
       </c>
       <c r="D109">
-        <v>3981168.738527122</v>
+        <v>3989352.085742486</v>
       </c>
       <c r="E109">
-        <v>5894079.004468725</v>
+        <v>5899446.575468102</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2224,13 +2224,13 @@
         <v>89466817.31530337</v>
       </c>
       <c r="C110">
-        <v>86046852.47278637</v>
+        <v>86155247.10948637</v>
       </c>
       <c r="D110">
-        <v>95394927.85009219</v>
+        <v>95591013.43913725</v>
       </c>
       <c r="E110">
-        <v>94492377.69068909</v>
+        <v>94578429.22575846</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2241,13 +2241,13 @@
         <v>15337168.68262343</v>
       </c>
       <c r="C111">
-        <v>19253577.48700469</v>
+        <v>19277831.53554805</v>
       </c>
       <c r="D111">
-        <v>27485376.48329302</v>
+        <v>27541873.05349139</v>
       </c>
       <c r="E111">
-        <v>38545405.55303357</v>
+        <v>38580507.76337869</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2255,16 +2255,16 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>3073170.725053974</v>
+        <v>3073292.903789499</v>
       </c>
       <c r="C112">
-        <v>4497910.298052996</v>
+        <v>4505620.552509816</v>
       </c>
       <c r="D112">
-        <v>7468945.03614437</v>
+        <v>7485228.241104241</v>
       </c>
       <c r="E112">
-        <v>11524630.25813952</v>
+        <v>11535840.91457181</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2275,13 +2275,13 @@
         <v>1465598.217597521</v>
       </c>
       <c r="C113">
-        <v>1626586.389497597</v>
+        <v>1628105.65885045</v>
       </c>
       <c r="D113">
-        <v>2119645.9753097</v>
+        <v>2124162.391714393</v>
       </c>
       <c r="E113">
-        <v>2419488.993334097</v>
+        <v>2421885.929870551</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2292,13 +2292,13 @@
         <v>2470904.223307132</v>
       </c>
       <c r="C114">
-        <v>3606436.97246527</v>
+        <v>3609722.573155822</v>
       </c>
       <c r="D114">
-        <v>6384764.399710033</v>
+        <v>6397459.027736069</v>
       </c>
       <c r="E114">
-        <v>9876046.034851715</v>
+        <v>9884884.647281798</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2306,16 +2306,16 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>6607317.058866044</v>
+        <v>6607579.743147423</v>
       </c>
       <c r="C115">
-        <v>8448777.451748196</v>
+        <v>8463260.227011682</v>
       </c>
       <c r="D115">
-        <v>11592425.10818241</v>
+        <v>11617697.99921388</v>
       </c>
       <c r="E115">
-        <v>15208733.37344641</v>
+        <v>15223527.76431197</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2323,16 +2323,16 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>4968292.672170592</v>
+        <v>4968490.19445969</v>
       </c>
       <c r="C116">
-        <v>6503735.160698252</v>
+        <v>6514883.771872303</v>
       </c>
       <c r="D116">
-        <v>9336181.295180464</v>
+        <v>9356535.301380303</v>
       </c>
       <c r="E116">
-        <v>12847128.81235225</v>
+        <v>12859625.93755546</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2343,13 +2343,13 @@
         <v>830505.6566385954</v>
       </c>
       <c r="C117">
-        <v>1161847.421069712</v>
+        <v>1162932.613464607</v>
       </c>
       <c r="D117">
-        <v>1665436.123457621</v>
+        <v>1668984.736347023</v>
       </c>
       <c r="E117">
-        <v>2326431.724359709</v>
+        <v>2328736.471029377</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2360,13 +2360,13 @@
         <v>700008.7702482764</v>
       </c>
       <c r="C118">
-        <v>661800.5949074012</v>
+        <v>662386.9332872819</v>
       </c>
       <c r="D118">
-        <v>859402.1874374202</v>
+        <v>860957.1017437766</v>
       </c>
       <c r="E118">
-        <v>1140055.12903061</v>
+        <v>1140964.116808932</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2377,13 +2377,13 @@
         <v>281353.1760897946</v>
       </c>
       <c r="C119">
-        <v>335403.9031571255</v>
+        <v>335576.4876365907</v>
       </c>
       <c r="D119">
-        <v>442200.5249967632</v>
+        <v>443113.268640707</v>
       </c>
       <c r="E119">
-        <v>549893.9723101233</v>
+        <v>550370.4209100871</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2391,16 +2391,16 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>19387776.95324304</v>
+        <v>19388065.23387093</v>
       </c>
       <c r="C120">
-        <v>29022267.48021519</v>
+        <v>29029845.97514856</v>
       </c>
       <c r="D120">
-        <v>42992533.06632285</v>
+        <v>43058082.66025158</v>
       </c>
       <c r="E120">
-        <v>60721161.29355522</v>
+        <v>60769496.64235567</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2408,16 +2408,16 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>22922565.0165415</v>
+        <v>22922905.85662087</v>
       </c>
       <c r="C121">
-        <v>24164463.05219634</v>
+        <v>24170773.04368593</v>
       </c>
       <c r="D121">
-        <v>27309231.53033212</v>
+        <v>27350869.2034266</v>
       </c>
       <c r="E121">
-        <v>29274587.87092087</v>
+        <v>29297891.07174224</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2428,13 +2428,13 @@
         <v>16075165.50305348</v>
       </c>
       <c r="C122">
-        <v>18728930.37551036</v>
+        <v>18740219.14047285</v>
       </c>
       <c r="D122">
-        <v>24554756.87454285</v>
+        <v>24604087.49974205</v>
       </c>
       <c r="E122">
-        <v>30985558.12788996</v>
+        <v>31015506.09496842</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2445,13 +2445,13 @@
         <v>6594939.693560401</v>
       </c>
       <c r="C123">
-        <v>8485599.522884954</v>
+        <v>8490714.173677022</v>
       </c>
       <c r="D123">
-        <v>11546123.92219883</v>
+        <v>11569320.14094454</v>
       </c>
       <c r="E123">
-        <v>15071525.25253862</v>
+        <v>15086092.08848917</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2462,13 +2462,13 @@
         <v>3709653.577627725</v>
       </c>
       <c r="C124">
-        <v>4303411.186605941</v>
+        <v>4306005.045221917</v>
       </c>
       <c r="D124">
-        <v>5080294.525767487</v>
+        <v>5090500.862015598</v>
       </c>
       <c r="E124">
-        <v>5710329.443508421</v>
+        <v>5715848.555266084</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2479,13 +2479,13 @@
         <v>7828594.622405516</v>
       </c>
       <c r="C125">
-        <v>9154597.449427089</v>
+        <v>9161707.282236667</v>
       </c>
       <c r="D125">
-        <v>12327807.2100273</v>
+        <v>12361817.68059009</v>
       </c>
       <c r="E125">
-        <v>15897369.07879983</v>
+        <v>15916708.7358476</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2496,13 +2496,13 @@
         <v>7403122.486757209</v>
       </c>
       <c r="C126">
-        <v>8271898.227471212</v>
+        <v>8278089.749266063</v>
       </c>
       <c r="D126">
-        <v>9178936.792116445</v>
+        <v>9202423.828258283</v>
       </c>
       <c r="E126">
-        <v>9210450.585371727</v>
+        <v>9220619.832122745</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2510,16 +2510,16 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>10548471.60703434</v>
+        <v>10548780.36459258</v>
       </c>
       <c r="C127">
-        <v>13801435.19431163</v>
+        <v>13818728.01129545</v>
       </c>
       <c r="D127">
-        <v>19173645.46525217</v>
+        <v>19221189.15288304</v>
       </c>
       <c r="E127">
-        <v>25636083.68265613</v>
+        <v>25659463.15477025</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2530,13 +2530,13 @@
         <v>1915505.434733891</v>
       </c>
       <c r="C128">
-        <v>2490298.578915408</v>
+        <v>2491783.269805439</v>
       </c>
       <c r="D128">
-        <v>3431467.893020432</v>
+        <v>3436502.34920756</v>
       </c>
       <c r="E128">
-        <v>4532374.729679327</v>
+        <v>4535865.25174793</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -2547,13 +2547,13 @@
         <v>12397576.84147213</v>
       </c>
       <c r="C129">
-        <v>15004048.93796533</v>
+        <v>15012994.20057777</v>
       </c>
       <c r="D129">
-        <v>19496976.66488882</v>
+        <v>19525581.52958841</v>
       </c>
       <c r="E129">
-        <v>24550363.11909636</v>
+        <v>24569270.11363462</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -2564,13 +2564,13 @@
         <v>3563738.577511906</v>
       </c>
       <c r="C130">
-        <v>5391530.487607346</v>
+        <v>5393191.331848907</v>
       </c>
       <c r="D130">
-        <v>8392492.542931221</v>
+        <v>8401216.275772359</v>
       </c>
       <c r="E130">
-        <v>12549912.3562161</v>
+        <v>12557658.82592667</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2581,13 +2581,13 @@
         <v>11447160.27928067</v>
       </c>
       <c r="C131">
-        <v>12642209.41921723</v>
+        <v>12646103.81261123</v>
       </c>
       <c r="D131">
-        <v>14475124.75294559</v>
+        <v>14490171.1912404</v>
       </c>
       <c r="E131">
-        <v>15921530.60116968</v>
+        <v>15931358.21199651</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2598,13 +2598,13 @@
         <v>24784181.92542371</v>
       </c>
       <c r="C132">
-        <v>32163268.08124382</v>
+        <v>32173175.8762021</v>
       </c>
       <c r="D132">
-        <v>41885467.37022555</v>
+        <v>41929006.00018498</v>
       </c>
       <c r="E132">
-        <v>53102987.35801888</v>
+        <v>53135765.33060014</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2615,13 +2615,13 @@
         <v>11771136.51359993</v>
       </c>
       <c r="C133">
-        <v>13881641.71521891</v>
+        <v>13885917.91188684</v>
       </c>
       <c r="D133">
-        <v>17169961.80801525</v>
+        <v>17187809.44492877</v>
       </c>
       <c r="E133">
-        <v>20510677.65680094</v>
+        <v>20523337.93192492</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2629,16 +2629,16 @@
         <v>133</v>
       </c>
       <c r="B134">
-        <v>7914275.428196833</v>
+        <v>7914282.976074042</v>
       </c>
       <c r="C134">
-        <v>14625939.67629747</v>
+        <v>14629289.32439217</v>
       </c>
       <c r="D134">
-        <v>33829989.0513148</v>
+        <v>33854278.53607288</v>
       </c>
       <c r="E134">
-        <v>64648417.86258776</v>
+        <v>64681904.93588045</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2649,13 +2649,13 @@
         <v>12468037.18155291</v>
       </c>
       <c r="C135">
-        <v>13764113.40055001</v>
+        <v>13769995.64788383</v>
       </c>
       <c r="D135">
-        <v>17790070.7864867</v>
+        <v>17812348.84864343</v>
       </c>
       <c r="E135">
-        <v>22971258.58472177</v>
+        <v>22987283.75844524</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2663,16 +2663,16 @@
         <v>135</v>
       </c>
       <c r="B136">
-        <v>15156354.48818463</v>
+        <v>15156950.55671404</v>
       </c>
       <c r="C136">
-        <v>21900113.59167534</v>
+        <v>21920088.56061206</v>
       </c>
       <c r="D136">
-        <v>33751354.94864237</v>
+        <v>33811762.76819921</v>
       </c>
       <c r="E136">
-        <v>49973917.64355537</v>
+        <v>50016730.92962685</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2680,16 +2680,16 @@
         <v>136</v>
       </c>
       <c r="B137">
-        <v>4010444.314743011</v>
+        <v>4010602.037343578</v>
       </c>
       <c r="C137">
-        <v>4966419.202483753</v>
+        <v>4970949.045166123</v>
       </c>
       <c r="D137">
-        <v>6554392.59047296</v>
+        <v>6566123.573288685</v>
       </c>
       <c r="E137">
-        <v>8514074.857790913</v>
+        <v>8521368.973195687</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2697,16 +2697,16 @@
         <v>137</v>
       </c>
       <c r="B138">
-        <v>10052152.63305716</v>
+        <v>10052547.96373131</v>
       </c>
       <c r="C138">
-        <v>11847602.43484076</v>
+        <v>11858408.56557702</v>
       </c>
       <c r="D138">
-        <v>15142907.01936856</v>
+        <v>15170009.63483937</v>
       </c>
       <c r="E138">
-        <v>18879035.55423203</v>
+        <v>18895209.46230348</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2717,13 +2717,13 @@
         <v>51362833.63044439</v>
       </c>
       <c r="C139">
-        <v>77807031.56271151</v>
+        <v>77864073.61799471</v>
       </c>
       <c r="D139">
-        <v>108359611.574423</v>
+        <v>108538707.2579393</v>
       </c>
       <c r="E139">
-        <v>143967770.0730123</v>
+        <v>144082838.0637922</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2731,16 +2731,16 @@
         <v>139</v>
       </c>
       <c r="B140">
-        <v>15582874.47515945</v>
+        <v>15583638.85236405</v>
       </c>
       <c r="C140">
-        <v>25158610.3292562</v>
+        <v>25188728.50696277</v>
       </c>
       <c r="D140">
-        <v>36594595.45113653</v>
+        <v>36675913.2875465</v>
       </c>
       <c r="E140">
-        <v>50091566.12748831</v>
+        <v>50143939.04008143</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -2751,13 +2751,13 @@
         <v>18176938.08964159</v>
       </c>
       <c r="C141">
-        <v>26434056.84144388</v>
+        <v>26453436.23301588</v>
       </c>
       <c r="D141">
-        <v>37048595.4792329</v>
+        <v>37109829.02773186</v>
       </c>
       <c r="E141">
-        <v>49959309.56350201</v>
+        <v>49999240.14914148</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2768,13 +2768,13 @@
         <v>2908310.094342655</v>
       </c>
       <c r="C142">
-        <v>4186389.09253636</v>
+        <v>4189458.226948217</v>
       </c>
       <c r="D142">
-        <v>7003088.169854999</v>
+        <v>7014662.804022485</v>
       </c>
       <c r="E142">
-        <v>11081547.40780082</v>
+        <v>11090404.4693105</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -2785,13 +2785,13 @@
         <v>13936848.09534258</v>
       </c>
       <c r="C143">
-        <v>22423810.37679196</v>
+        <v>22438064.63103374</v>
       </c>
       <c r="D143">
-        <v>36836672.90268905</v>
+        <v>36899579.78239022</v>
       </c>
       <c r="E143">
-        <v>56887789.97518899</v>
+        <v>56940864.80422375</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -2802,13 +2802,13 @@
         <v>5219793.294135799</v>
       </c>
       <c r="C144">
-        <v>7252984.48845023</v>
+        <v>7257595.02890579</v>
       </c>
       <c r="D144">
-        <v>11975708.47453677</v>
+        <v>11996159.68234085</v>
       </c>
       <c r="E144">
-        <v>18962596.65839633</v>
+        <v>18980288.26807458</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -2819,13 +2819,13 @@
         <v>6420345.751787032</v>
       </c>
       <c r="C145">
-        <v>10939918.2700791</v>
+        <v>10946872.5019329</v>
       </c>
       <c r="D145">
-        <v>22814482.60022511</v>
+        <v>22853443.44547213</v>
       </c>
       <c r="E145">
-        <v>41532711.70546318</v>
+        <v>41571460.6456853</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -2836,13 +2836,13 @@
         <v>10322445.95384374</v>
       </c>
       <c r="C146">
-        <v>16685000.47873323</v>
+        <v>16694947.90769644</v>
       </c>
       <c r="D146">
-        <v>23552347.81118569</v>
+        <v>23586902.4877428</v>
       </c>
       <c r="E146">
-        <v>31348925.21361535</v>
+        <v>31373067.99125652</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -2853,13 +2853,13 @@
         <v>9669524.608203672</v>
       </c>
       <c r="C147">
-        <v>13086626.08623777</v>
+        <v>13096713.6334371</v>
       </c>
       <c r="D147">
-        <v>21609470.0514775</v>
+        <v>21647222.97600459</v>
       </c>
       <c r="E147">
-        <v>34603277.58877786</v>
+        <v>34636742.58503096</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -2870,13 +2870,13 @@
         <v>8398610.504290925</v>
       </c>
       <c r="C148">
-        <v>10583451.21785698</v>
+        <v>10591752.79136544</v>
       </c>
       <c r="D148">
-        <v>14360115.4378935</v>
+        <v>14387130.36626752</v>
       </c>
       <c r="E148">
-        <v>19172889.29233149</v>
+        <v>19193032.30334736</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -2887,13 +2887,13 @@
         <v>5364917.450563887</v>
       </c>
       <c r="C149">
-        <v>6007376.010138847</v>
+        <v>6009062.03697775</v>
       </c>
       <c r="D149">
-        <v>7655160.271570844</v>
+        <v>7661771.489491164</v>
       </c>
       <c r="E149">
-        <v>9795022.678194186</v>
+        <v>9802645.531489145</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -2904,13 +2904,13 @@
         <v>2874062.919944939</v>
       </c>
       <c r="C150">
-        <v>3495200.587717147</v>
+        <v>3496181.548787055</v>
       </c>
       <c r="D150">
-        <v>4662688.529047696</v>
+        <v>4666715.361780982</v>
       </c>
       <c r="E150">
-        <v>6209344.733498099</v>
+        <v>6214177.077997583</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -2921,13 +2921,13 @@
         <v>22609294.97023352</v>
       </c>
       <c r="C151">
-        <v>24357179.09565387</v>
+        <v>24364015.16810979</v>
       </c>
       <c r="D151">
-        <v>26723468.58439276</v>
+        <v>26746547.74513279</v>
       </c>
       <c r="E151">
-        <v>26936312.36503401</v>
+        <v>26957275.21159515</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -2938,13 +2938,13 @@
         <v>5748125.839889878</v>
       </c>
       <c r="C152">
-        <v>7372688.739715857</v>
+        <v>7374757.954472694</v>
       </c>
       <c r="D152">
-        <v>9951708.353042098</v>
+        <v>9960302.936338512</v>
       </c>
       <c r="E152">
-        <v>13205789.5036368</v>
+        <v>13216066.74334697</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -2955,13 +2955,13 @@
         <v>36184364.91961887</v>
       </c>
       <c r="C153">
-        <v>39889886.68835727</v>
+        <v>39945045.66501394</v>
       </c>
       <c r="D153">
-        <v>50039259.36203168</v>
+        <v>50173931.12916134</v>
       </c>
       <c r="E153">
-        <v>59698828.43465899</v>
+        <v>59780607.60460003</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -2972,13 +2972,13 @@
         <v>7254897.57417016</v>
       </c>
       <c r="C154">
-        <v>9416975.90255649</v>
+        <v>9429997.517735386</v>
       </c>
       <c r="D154">
-        <v>13245686.30171427</v>
+        <v>13281334.71066036</v>
       </c>
       <c r="E154">
-        <v>17820545.80139074</v>
+        <v>17844957.49391046</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -2989,13 +2989,13 @@
         <v>18281283.84109003</v>
       </c>
       <c r="C155">
-        <v>20454778.38239207</v>
+        <v>20467700.74206372</v>
       </c>
       <c r="D155">
-        <v>26750105.63397881</v>
+        <v>26835218.10462372</v>
       </c>
       <c r="E155">
-        <v>34140935.84681761</v>
+        <v>34201869.47308409</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3006,13 +3006,13 @@
         <v>6079589.742502036</v>
       </c>
       <c r="C156">
-        <v>7554042.85584743</v>
+        <v>7558815.142153028</v>
       </c>
       <c r="D156">
-        <v>10388390.5374675</v>
+        <v>10421443.92412572</v>
       </c>
       <c r="E156">
-        <v>13959101.84869882</v>
+        <v>13984015.59736936</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3023,13 +3023,13 @@
         <v>6222495.324174391</v>
       </c>
       <c r="C157">
-        <v>7366701.801374334</v>
+        <v>7371272.774790601</v>
       </c>
       <c r="D157">
-        <v>10030661.29165106</v>
+        <v>10060740.85873055</v>
       </c>
       <c r="E157">
-        <v>13468049.35597329</v>
+        <v>13490508.72730011</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3040,13 +3040,13 @@
         <v>18199723.66899363</v>
       </c>
       <c r="C158">
-        <v>22028102.99457411</v>
+        <v>22041889.82116809</v>
       </c>
       <c r="D158">
-        <v>28924428.67881685</v>
+        <v>28969659.3237275</v>
       </c>
       <c r="E158">
-        <v>36704158.87836814</v>
+        <v>36746465.27613227</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3057,13 +3057,13 @@
         <v>16269007.47227691</v>
       </c>
       <c r="C159">
-        <v>20822140.00545043</v>
+        <v>20835366.75989526</v>
       </c>
       <c r="D159">
-        <v>31237915.57250169</v>
+        <v>31288913.39699925</v>
       </c>
       <c r="E159">
-        <v>46631011.98510846</v>
+        <v>46688174.14632989</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3074,13 +3074,13 @@
         <v>2785236.386868545</v>
       </c>
       <c r="C160">
-        <v>3565035.779611628</v>
+        <v>3566443.101156476</v>
       </c>
       <c r="D160">
-        <v>5229797.641750151</v>
+        <v>5241485.110747285</v>
       </c>
       <c r="E160">
-        <v>7528101.438565345</v>
+        <v>7539476.847427968</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3088,16 +3088,16 @@
         <v>160</v>
       </c>
       <c r="B161">
-        <v>12743269.20457114</v>
+        <v>12745073.59984315</v>
       </c>
       <c r="C161">
-        <v>16898853.95625263</v>
+        <v>16933272.22455894</v>
       </c>
       <c r="D161">
-        <v>25091561.41398896</v>
+        <v>25168644.98421092</v>
       </c>
       <c r="E161">
-        <v>35847746.15735371</v>
+        <v>35906502.11840332</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3108,13 +3108,13 @@
         <v>7748208.555374418</v>
       </c>
       <c r="C162">
-        <v>12676299.47775152</v>
+        <v>12681109.19699587</v>
       </c>
       <c r="D162">
-        <v>21669693.49453345</v>
+        <v>21712001.2687281</v>
       </c>
       <c r="E162">
-        <v>34973149.21651921</v>
+        <v>35019271.09847495</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3125,13 +3125,13 @@
         <v>9612492.333800167</v>
       </c>
       <c r="C163">
-        <v>11950766.22098832</v>
+        <v>11956027.11924812</v>
       </c>
       <c r="D163">
-        <v>15956038.28396906</v>
+        <v>15984854.15686291</v>
       </c>
       <c r="E163">
-        <v>21916253.82247059</v>
+        <v>21940432.21682576</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3142,13 +3142,13 @@
         <v>1224363.449586149</v>
       </c>
       <c r="C164">
-        <v>1972211.385079622</v>
+        <v>1973064.872724676</v>
       </c>
       <c r="D164">
-        <v>3224785.124996874</v>
+        <v>3230318.740726369</v>
       </c>
       <c r="E164">
-        <v>5008879.881558501</v>
+        <v>5014040.024797849</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3159,13 +3159,13 @@
         <v>10251063.40552132</v>
       </c>
       <c r="C165">
-        <v>12000505.85368921</v>
+        <v>12008893.7251472</v>
       </c>
       <c r="D165">
-        <v>15501264.83491633</v>
+        <v>15540499.41576367</v>
       </c>
       <c r="E165">
-        <v>19334817.8172849</v>
+        <v>19362655.42428816</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3176,13 +3176,13 @@
         <v>3866629.179275585</v>
       </c>
       <c r="C166">
-        <v>5478491.802771163</v>
+        <v>5482321.048436764</v>
       </c>
       <c r="D166">
-        <v>9178380.494358353</v>
+        <v>9201611.496175855</v>
       </c>
       <c r="E166">
-        <v>14846377.96684377</v>
+        <v>14867753.27222127</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3193,13 +3193,13 @@
         <v>17821287.4398209</v>
       </c>
       <c r="C167">
-        <v>22661384.42159159</v>
+        <v>22695925.75016938</v>
       </c>
       <c r="D167">
-        <v>33888776.1224847</v>
+        <v>33973866.27750613</v>
       </c>
       <c r="E167">
-        <v>50111697.2823183</v>
+        <v>50172076.42655051</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3210,13 +3210,13 @@
         <v>1035903.522599032</v>
       </c>
       <c r="C168">
-        <v>1024832.258794348</v>
+        <v>1026354.203919581</v>
       </c>
       <c r="D168">
-        <v>1148121.721604813</v>
+        <v>1150766.311843366</v>
       </c>
       <c r="E168">
-        <v>1086737.453450788</v>
+        <v>1087927.408109399</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3227,13 +3227,13 @@
         <v>7939973.422334475</v>
       </c>
       <c r="C169">
-        <v>10836662.11176032</v>
+        <v>10839473.4251954</v>
       </c>
       <c r="D169">
-        <v>15388984.93049095</v>
+        <v>15410060.13772783</v>
       </c>
       <c r="E169">
-        <v>21339925.52573091</v>
+        <v>21354440.08091369</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3244,13 +3244,13 @@
         <v>18084604.9308377</v>
       </c>
       <c r="C170">
-        <v>25490240.31452638</v>
+        <v>25492372.12983827</v>
       </c>
       <c r="D170">
-        <v>37473913.94723814</v>
+        <v>37511062.24755383</v>
       </c>
       <c r="E170">
-        <v>53298878.40566178</v>
+        <v>53333922.11355664</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3261,13 +3261,13 @@
         <v>6859704.929499852</v>
       </c>
       <c r="C171">
-        <v>8656873.755946465</v>
+        <v>8659119.57529977</v>
       </c>
       <c r="D171">
-        <v>13212764.83931042</v>
+        <v>13230859.71421076</v>
       </c>
       <c r="E171">
-        <v>19640285.43961075</v>
+        <v>19653643.96827454</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3278,13 +3278,13 @@
         <v>6552393.090883224</v>
       </c>
       <c r="C172">
-        <v>7557106.540306645</v>
+        <v>7557738.560846168</v>
       </c>
       <c r="D172">
-        <v>9141821.749225434</v>
+        <v>9150884.137004059</v>
       </c>
       <c r="E172">
-        <v>10603965.33725208</v>
+        <v>10610937.38384897</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3295,13 +3295,13 @@
         <v>16302354.01011746</v>
       </c>
       <c r="C173">
-        <v>20872008.53989454</v>
+        <v>20873754.12043227</v>
       </c>
       <c r="D173">
-        <v>31203077.54074466</v>
+        <v>31234009.49241881</v>
       </c>
       <c r="E173">
-        <v>45857499.22162523</v>
+        <v>45887650.26524158</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3312,13 +3312,13 @@
         <v>32478889.67846984</v>
       </c>
       <c r="C174">
-        <v>43033735.74850929</v>
+        <v>43037900.11262348</v>
       </c>
       <c r="D174">
-        <v>64097887.29156983</v>
+        <v>64140665.65311423</v>
       </c>
       <c r="E174">
-        <v>93735835.72423968</v>
+        <v>93784119.43043241</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3326,16 +3326,16 @@
         <v>174</v>
       </c>
       <c r="B175">
-        <v>157516437.7447567</v>
+        <v>157522497.479256</v>
       </c>
       <c r="C175">
-        <v>166823743.1065215</v>
+        <v>166919086.983405</v>
       </c>
       <c r="D175">
-        <v>195312589.6995636</v>
+        <v>195619164.6169351</v>
       </c>
       <c r="E175">
-        <v>216905915.4988078</v>
+        <v>217059660.4124538</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3343,16 +3343,16 @@
         <v>175</v>
       </c>
       <c r="B176">
-        <v>16560793.8200223</v>
+        <v>16561437.1893122</v>
       </c>
       <c r="C176">
-        <v>20372504.8128094</v>
+        <v>20384541.66903715</v>
       </c>
       <c r="D176">
-        <v>27535098.38711163</v>
+        <v>27581376.60303943</v>
       </c>
       <c r="E176">
-        <v>36194718.17999303</v>
+        <v>36223436.57997105</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3360,16 +3360,16 @@
         <v>176</v>
       </c>
       <c r="B177">
-        <v>11437298.2319529</v>
+        <v>11437742.55886874</v>
       </c>
       <c r="C177">
-        <v>17668190.01464886</v>
+        <v>17678629.05810301</v>
       </c>
       <c r="D177">
-        <v>29217798.84410179</v>
+        <v>29266905.17322517</v>
       </c>
       <c r="E177">
-        <v>45313906.91625102</v>
+        <v>45349860.86115856</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3380,13 +3380,13 @@
         <v>4715143.758782363</v>
       </c>
       <c r="C178">
-        <v>6789174.588278342</v>
+        <v>6791582.416521139</v>
       </c>
       <c r="D178">
-        <v>10464765.50569098</v>
+        <v>10479030.89395642</v>
       </c>
       <c r="E178">
-        <v>15586225.0699687</v>
+        <v>15598337.86261776</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3397,13 +3397,13 @@
         <v>18899418.38154183</v>
       </c>
       <c r="C179">
-        <v>22991409.52630343</v>
+        <v>23005941.87561277</v>
       </c>
       <c r="D179">
-        <v>33866489.96768139</v>
+        <v>33916277.85658064</v>
       </c>
       <c r="E179">
-        <v>47466459.02243701</v>
+        <v>47503465.07185429</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3414,13 +3414,13 @@
         <v>730916.2387789158</v>
       </c>
       <c r="C180">
-        <v>851851.6138945379</v>
+        <v>852347.0606603625</v>
       </c>
       <c r="D180">
-        <v>2163521.204055536</v>
+        <v>2166265.277393222</v>
       </c>
       <c r="E180">
-        <v>2649271.511766691</v>
+        <v>2650909.199498853</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3431,13 +3431,13 @@
         <v>104416.6055398451</v>
       </c>
       <c r="C181">
-        <v>121693.0876992197</v>
+        <v>121763.8658086232</v>
       </c>
       <c r="D181">
-        <v>77268.61443055485</v>
+        <v>77366.61704975793</v>
       </c>
       <c r="E181">
-        <v>94616.83970595326</v>
+        <v>94675.32855353045</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3445,16 +3445,16 @@
         <v>181</v>
       </c>
       <c r="B182">
-        <v>73942226.40146619</v>
+        <v>73945119.30512773</v>
       </c>
       <c r="C182">
-        <v>76542593.40538403</v>
+        <v>76658457.25897783</v>
       </c>
       <c r="D182">
-        <v>94523507.4746846</v>
+        <v>94785186.83952728</v>
       </c>
       <c r="E182">
-        <v>111086653.1272785</v>
+        <v>111250106.0041151</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3465,13 +3465,13 @@
         <v>4201919.443994937</v>
       </c>
       <c r="C183">
-        <v>3622764.221663627</v>
+        <v>3623513.717951481</v>
       </c>
       <c r="D183">
-        <v>3729944.6958802</v>
+        <v>3739974.634699902</v>
       </c>
       <c r="E183">
-        <v>3336187.580277742</v>
+        <v>3342427.681942746</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3482,13 +3482,13 @@
         <v>966311.5224508207</v>
       </c>
       <c r="C184">
-        <v>1019451.164015462</v>
+        <v>1019655.313458947</v>
       </c>
       <c r="D184">
-        <v>1031082.523931491</v>
+        <v>1032796.438734183</v>
       </c>
       <c r="E184">
-        <v>829243.0409641388</v>
+        <v>829988.883654924</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3499,13 +3499,13 @@
         <v>12465418.63961559</v>
       </c>
       <c r="C185">
-        <v>15801493.04223966</v>
+        <v>15804657.35861367</v>
       </c>
       <c r="D185">
-        <v>21947328.00939887</v>
+        <v>21983809.91019905</v>
       </c>
       <c r="E185">
-        <v>30221301.93735972</v>
+        <v>30248483.75986834</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3516,13 +3516,13 @@
         <v>5625911.501370947</v>
       </c>
       <c r="C186">
-        <v>7640386.848664692</v>
+        <v>7641467.050587453</v>
       </c>
       <c r="D186">
-        <v>11321959.5996812</v>
+        <v>11335421.69494418</v>
       </c>
       <c r="E186">
-        <v>16564130.45602662</v>
+        <v>16578451.3291986</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -3533,13 +3533,13 @@
         <v>2361215.666680087</v>
       </c>
       <c r="C187">
-        <v>3079458.17916291</v>
+        <v>3079913.006402222</v>
       </c>
       <c r="D187">
-        <v>4664819.663910083</v>
+        <v>4670615.00344638</v>
       </c>
       <c r="E187">
-        <v>6848167.989052576</v>
+        <v>6854632.102596479</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3550,13 +3550,13 @@
         <v>6138456.118865858</v>
       </c>
       <c r="C188">
-        <v>6425018.652891322</v>
+        <v>6432663.980670236</v>
       </c>
       <c r="D188">
-        <v>7721588.664719691</v>
+        <v>7747300.048709562</v>
       </c>
       <c r="E188">
-        <v>8625019.670497006</v>
+        <v>8638544.362418586</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -3567,13 +3567,13 @@
         <v>84746023.68419842</v>
       </c>
       <c r="C189">
-        <v>98934840.0697249</v>
+        <v>99052565.6860929</v>
       </c>
       <c r="D189">
-        <v>135057605.3720062</v>
+        <v>135507320.8519745</v>
       </c>
       <c r="E189">
-        <v>177351966.9745947</v>
+        <v>177630068.4522322</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3584,13 +3584,13 @@
         <v>27071033.09974656</v>
       </c>
       <c r="C190">
-        <v>36565146.80507256</v>
+        <v>36608656.80056232</v>
       </c>
       <c r="D190">
-        <v>50681700.14479651</v>
+        <v>50850460.31971185</v>
       </c>
       <c r="E190">
-        <v>68820469.45417403</v>
+        <v>68928385.22513165</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3601,13 +3601,13 @@
         <v>1255779.146554206</v>
       </c>
       <c r="C191">
-        <v>1706222.817136904</v>
+        <v>1707080.849844529</v>
       </c>
       <c r="D191">
-        <v>2516253.349795789</v>
+        <v>2521077.296443145</v>
       </c>
       <c r="E191">
-        <v>3509529.482790135</v>
+        <v>3512894.25809167</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3618,13 +3618,13 @@
         <v>5969866.025191164</v>
       </c>
       <c r="C192">
-        <v>7254994.693282111</v>
+        <v>7256066.235422185</v>
       </c>
       <c r="D192">
-        <v>9886632.72052585</v>
+        <v>9898915.380438596</v>
       </c>
       <c r="E192">
-        <v>12629089.01877228</v>
+        <v>12641009.85154156</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3635,13 +3635,13 @@
         <v>14887088.96011864</v>
       </c>
       <c r="C193">
-        <v>19168706.37741104</v>
+        <v>19173255.27918717</v>
       </c>
       <c r="D193">
-        <v>27391399.89086554</v>
+        <v>27422298.17645163</v>
       </c>
       <c r="E193">
-        <v>37298617.88181955</v>
+        <v>37325212.7107677</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3652,13 +3652,13 @@
         <v>9091757.900643885</v>
       </c>
       <c r="C194">
-        <v>11919003.32441584</v>
+        <v>11921831.80821253</v>
       </c>
       <c r="D194">
-        <v>17951425.91717742</v>
+        <v>17971675.64106435</v>
       </c>
       <c r="E194">
-        <v>26466948.54745276</v>
+        <v>26485820.13062051</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3669,13 +3669,13 @@
         <v>24414067.93806247</v>
       </c>
       <c r="C195">
-        <v>38800232.73348667</v>
+        <v>38810298.52814213</v>
       </c>
       <c r="D195">
-        <v>57592110.27017069</v>
+        <v>57670982.63664808</v>
       </c>
       <c r="E195">
-        <v>81960421.93068331</v>
+        <v>82016168.09837647</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3686,13 +3686,13 @@
         <v>5741200.172614049</v>
       </c>
       <c r="C196">
-        <v>7693271.8720681</v>
+        <v>7695047.187416097</v>
       </c>
       <c r="D196">
-        <v>12052104.90675539</v>
+        <v>12071765.01388881</v>
       </c>
       <c r="E196">
-        <v>18298011.78754391</v>
+        <v>18314265.04711291</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3703,13 +3703,13 @@
         <v>11551463.34366341</v>
       </c>
       <c r="C197">
-        <v>14223037.0396378</v>
+        <v>14229077.84373286</v>
       </c>
       <c r="D197">
-        <v>18571482.60557823</v>
+        <v>18603483.15250715</v>
       </c>
       <c r="E197">
-        <v>22727799.30570387</v>
+        <v>22748491.09572885</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3720,13 +3720,13 @@
         <v>3784100.060855254</v>
       </c>
       <c r="C198">
-        <v>4798829.5702843</v>
+        <v>4800867.727763527</v>
       </c>
       <c r="D198">
-        <v>6488831.271828539</v>
+        <v>6500012.185815752</v>
       </c>
       <c r="E198">
-        <v>8315048.526477024</v>
+        <v>8322618.693559335</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3737,13 +3737,13 @@
         <v>9303507.196704976</v>
       </c>
       <c r="C199">
-        <v>10869300.02382076</v>
+        <v>10873810.41857971</v>
       </c>
       <c r="D199">
-        <v>13939281.47453096</v>
+        <v>13962007.73502684</v>
       </c>
       <c r="E199">
-        <v>16810954.08290916</v>
+        <v>16824943.68930801</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3754,13 +3754,13 @@
         <v>7291938.073093089</v>
       </c>
       <c r="C200">
-        <v>10458029.21210863</v>
+        <v>10462368.9432821</v>
       </c>
       <c r="D200">
-        <v>15302906.83616985</v>
+        <v>15327856.31780121</v>
       </c>
       <c r="E200">
-        <v>21480663.55038393</v>
+        <v>21498539.15856024</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3771,13 +3771,13 @@
         <v>8220671.435856983</v>
       </c>
       <c r="C201">
-        <v>11756350.68993259</v>
+        <v>11756610.39653695</v>
       </c>
       <c r="D201">
-        <v>16233216.68190942</v>
+        <v>16248410.02265481</v>
       </c>
       <c r="E201">
-        <v>21073432.82554186</v>
+        <v>21088916.70598861</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -3788,13 +3788,13 @@
         <v>59568773.04269265</v>
       </c>
       <c r="C202">
-        <v>99868341.33040817</v>
+        <v>99902322.85591403</v>
       </c>
       <c r="D202">
-        <v>185160122.1120161</v>
+        <v>185489619.2353089</v>
       </c>
       <c r="E202">
-        <v>305908767.8802919</v>
+        <v>306180828.1926895</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -3805,13 +3805,13 @@
         <v>21591479.83760489</v>
       </c>
       <c r="C203">
-        <v>26878491.98628067</v>
+        <v>26884578.14254591</v>
       </c>
       <c r="D203">
-        <v>38043659.5636885</v>
+        <v>38102617.47239577</v>
       </c>
       <c r="E203">
-        <v>52508835.8707229</v>
+        <v>52551514.74339046</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -3822,13 +3822,13 @@
         <v>7849506.916002085</v>
       </c>
       <c r="C204">
-        <v>9640354.600115297</v>
+        <v>9643602.485039245</v>
       </c>
       <c r="D204">
-        <v>12623113.70285857</v>
+        <v>12648234.18479685</v>
       </c>
       <c r="E204">
-        <v>15756388.04526007</v>
+        <v>15770955.86234225</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -3839,13 +3839,13 @@
         <v>967432.2579188669</v>
       </c>
       <c r="C205">
-        <v>1317808.271697104</v>
+        <v>1318240.832942851</v>
       </c>
       <c r="D205">
-        <v>1873575.027001564</v>
+        <v>1877093.332276409</v>
       </c>
       <c r="E205">
-        <v>2607485.871754876</v>
+        <v>2609661.334516709</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -3853,16 +3853,16 @@
         <v>205</v>
       </c>
       <c r="B206">
-        <v>27511692.14556869</v>
+        <v>27511822.49256264</v>
       </c>
       <c r="C206">
-        <v>34799254.6343855</v>
+        <v>34809212.5288235</v>
       </c>
       <c r="D206">
-        <v>42532857.6560721</v>
+        <v>42625858.18149799</v>
       </c>
       <c r="E206">
-        <v>46571111.1583029</v>
+        <v>46756665.2543731</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -3870,16 +3870,16 @@
         <v>206</v>
       </c>
       <c r="B207">
-        <v>3569140.061287465</v>
+        <v>3569218.29044506</v>
       </c>
       <c r="C207">
-        <v>4587274.501573218</v>
+        <v>4588634.924134292</v>
       </c>
       <c r="D207">
-        <v>5991334.673558454</v>
+        <v>6011425.549612325</v>
       </c>
       <c r="E207">
-        <v>7096823.933262048</v>
+        <v>7146236.247112274</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -3887,16 +3887,16 @@
         <v>207</v>
       </c>
       <c r="B208">
-        <v>3253286.958518662</v>
+        <v>3253358.264741957</v>
       </c>
       <c r="C208">
-        <v>4382485.461324413</v>
+        <v>4383785.15073544</v>
       </c>
       <c r="D208">
-        <v>6105455.334007187</v>
+        <v>6125928.893414464</v>
       </c>
       <c r="E208">
-        <v>7762151.177005365</v>
+        <v>7816195.895279049</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -3904,16 +3904,16 @@
         <v>208</v>
       </c>
       <c r="B209">
-        <v>22950168.05925678</v>
+        <v>22950276.79431392</v>
       </c>
       <c r="C209">
-        <v>31172419.38884928</v>
+        <v>31181339.45523899</v>
       </c>
       <c r="D209">
-        <v>44214244.41553615</v>
+        <v>44310921.38925853</v>
       </c>
       <c r="E209">
-        <v>58826666.72627734</v>
+        <v>59061050.84762917</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -3921,16 +3921,16 @@
         <v>209</v>
       </c>
       <c r="B210">
-        <v>2589995.442704178</v>
+        <v>2590052.210765441</v>
       </c>
       <c r="C210">
-        <v>4095780.804976088</v>
+        <v>4096995.467977046</v>
       </c>
       <c r="D210">
-        <v>6390756.985129018</v>
+        <v>6412187.252919813</v>
       </c>
       <c r="E210">
-        <v>9240656.163101625</v>
+        <v>9304995.11342744</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -3941,13 +3941,13 @@
         <v>46707151.36189535</v>
       </c>
       <c r="C211">
-        <v>51972070.34031313</v>
+        <v>51989872.88817828</v>
       </c>
       <c r="D211">
-        <v>65266016.42450618</v>
+        <v>65399465.32710663</v>
       </c>
       <c r="E211">
-        <v>75692836.56672011</v>
+        <v>76108456.47961792</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -3955,16 +3955,16 @@
         <v>211</v>
       </c>
       <c r="B212">
-        <v>17303200.55214769</v>
+        <v>17303879.0390278</v>
       </c>
       <c r="C212">
-        <v>21265850.65063312</v>
+        <v>21276745.1171051</v>
       </c>
       <c r="D212">
-        <v>29230623.30616127</v>
+        <v>29402164.51069617</v>
       </c>
       <c r="E212">
-        <v>37563739.58964956</v>
+        <v>37831874.95442413</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -3972,16 +3972,16 @@
         <v>212</v>
       </c>
       <c r="B213">
-        <v>2937433.85574986</v>
+        <v>2937498.239038854</v>
       </c>
       <c r="C213">
-        <v>4054822.996926327</v>
+        <v>4056025.513297276</v>
       </c>
       <c r="D213">
-        <v>6162515.664231553</v>
+        <v>6183180.565315533</v>
       </c>
       <c r="E213">
-        <v>8871029.916577559</v>
+        <v>8932795.308890343</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -3992,13 +3992,13 @@
         <v>2093960.176027421</v>
       </c>
       <c r="C214">
-        <v>2772350.671834976</v>
+        <v>2772451.825460935</v>
       </c>
       <c r="D214">
-        <v>3871976.061992382</v>
+        <v>3878620.751812775</v>
       </c>
       <c r="E214">
-        <v>4891485.037912324</v>
+        <v>4919544.448913608</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4009,13 +4009,13 @@
         <v>1744966.813356184</v>
       </c>
       <c r="C215">
-        <v>2472637.085690654</v>
+        <v>2472727.303789483</v>
       </c>
       <c r="D215">
-        <v>3978057.597937379</v>
+        <v>3984884.334054221</v>
       </c>
       <c r="E215">
-        <v>6009538.760863713</v>
+        <v>6044011.751522432</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4026,13 +4026,13 @@
         <v>6402074.613295347</v>
       </c>
       <c r="C216">
-        <v>8660671.227264291</v>
+        <v>8661538.161777737</v>
       </c>
       <c r="D216">
-        <v>11994601.26876972</v>
+        <v>12020276.51494374</v>
       </c>
       <c r="E216">
-        <v>15386886.91114096</v>
+        <v>15487282.4088547</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4043,13 +4043,13 @@
         <v>2581711.68371857</v>
       </c>
       <c r="C217">
-        <v>4497478.893293728</v>
+        <v>4498180.564175085</v>
       </c>
       <c r="D217">
-        <v>9644779.744535999</v>
+        <v>9669828.319641836</v>
       </c>
       <c r="E217">
-        <v>17970063.04214356</v>
+        <v>18089977.47798312</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4060,13 +4060,13 @@
         <v>5170299.620711505</v>
       </c>
       <c r="C218">
-        <v>6536643.724973276</v>
+        <v>6537599.546286605</v>
       </c>
       <c r="D218">
-        <v>8932008.388951026</v>
+        <v>8954053.591853024</v>
       </c>
       <c r="E218">
-        <v>11017371.49631409</v>
+        <v>11086887.02095516</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4077,13 +4077,13 @@
         <v>5209390.470468674</v>
       </c>
       <c r="C219">
-        <v>6935870.919526733</v>
+        <v>6937233.913698304</v>
       </c>
       <c r="D219">
-        <v>9448444.762915682</v>
+        <v>9474421.601539843</v>
       </c>
       <c r="E219">
-        <v>11615400.6510204</v>
+        <v>11671328.95477457</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4091,16 +4091,16 @@
         <v>219</v>
       </c>
       <c r="B220">
-        <v>5388602.024114388</v>
+        <v>5388856.30932662</v>
       </c>
       <c r="C220">
-        <v>7191244.889004256</v>
+        <v>7200512.225741808</v>
       </c>
       <c r="D220">
-        <v>10356184.1981313</v>
+        <v>10431447.44493876</v>
       </c>
       <c r="E220">
-        <v>13761005.04906419</v>
+        <v>13853299.17269655</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4111,13 +4111,13 @@
         <v>4166980.951278996</v>
       </c>
       <c r="C221">
-        <v>5078196.814002733</v>
+        <v>5078852.204565376</v>
       </c>
       <c r="D221">
-        <v>6585752.354940008</v>
+        <v>6598378.989864132</v>
       </c>
       <c r="E221">
-        <v>7832112.876426782</v>
+        <v>7853225.626437086</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4128,13 +4128,13 @@
         <v>3977440.021371352</v>
       </c>
       <c r="C222">
-        <v>5847891.167444107</v>
+        <v>5849040.358608373</v>
       </c>
       <c r="D222">
-        <v>9823879.654157363</v>
+        <v>9850888.685044738</v>
       </c>
       <c r="E222">
-        <v>15380392.58617873</v>
+        <v>15454449.37459805</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4145,13 +4145,13 @@
         <v>5109053.86096241</v>
       </c>
       <c r="C223">
-        <v>5483475.705750718</v>
+        <v>5484154.354040458</v>
       </c>
       <c r="D223">
-        <v>6317169.982167263</v>
+        <v>6328491.734578871</v>
       </c>
       <c r="E223">
-        <v>6352556.519536261</v>
+        <v>6368624.606365709</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4165,10 +4165,10 @@
         <v>3805604.157880947</v>
       </c>
       <c r="D224">
-        <v>5487500.791433522</v>
+        <v>5488719.075824425</v>
       </c>
       <c r="E224">
-        <v>7329188.878931041</v>
+        <v>7340022.977728853</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4179,13 +4179,13 @@
         <v>3198141.980684864</v>
       </c>
       <c r="C225">
-        <v>3894521.971900282</v>
+        <v>3894526.400234907</v>
       </c>
       <c r="D225">
-        <v>5101552.126155938</v>
+        <v>5103200.352987189</v>
       </c>
       <c r="E225">
-        <v>6049669.127430283</v>
+        <v>6059831.679514278</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4196,13 +4196,13 @@
         <v>2687173.503213845</v>
       </c>
       <c r="C226">
-        <v>3703094.682105043</v>
+        <v>3703096.859897097</v>
       </c>
       <c r="D226">
-        <v>5422494.391105259</v>
+        <v>5423984.883787513</v>
       </c>
       <c r="E226">
-        <v>7367362.107379559</v>
+        <v>7379015.390568142</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4213,13 +4213,13 @@
         <v>2992855.305768633</v>
       </c>
       <c r="C227">
-        <v>3886930.279475303</v>
+        <v>3887157.117577421</v>
       </c>
       <c r="D227">
-        <v>5939666.475215647</v>
+        <v>5942657.179524695</v>
       </c>
       <c r="E227">
-        <v>8734958.230794769</v>
+        <v>8748207.008844003</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4230,13 +4230,13 @@
         <v>26411221.05406759</v>
       </c>
       <c r="C228">
-        <v>29190906.93813987</v>
+        <v>29193696.25293475</v>
       </c>
       <c r="D228">
-        <v>35491660.84686818</v>
+        <v>35532061.58525501</v>
       </c>
       <c r="E228">
-        <v>36210426.68915814</v>
+        <v>36371680.80790094</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4244,16 +4244,16 @@
         <v>228</v>
       </c>
       <c r="B229">
-        <v>5212503.918751173</v>
+        <v>5212749.893989149</v>
       </c>
       <c r="C229">
-        <v>7424726.865919978</v>
+        <v>7434295.090213945</v>
       </c>
       <c r="D229">
-        <v>10485636.50060794</v>
+        <v>10561840.53800049</v>
       </c>
       <c r="E229">
-        <v>13348998.90987065</v>
+        <v>13438529.73638827</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4264,13 +4264,13 @@
         <v>4184991.506479357</v>
       </c>
       <c r="C230">
-        <v>4925725.397334653</v>
+        <v>4926378.794247348</v>
       </c>
       <c r="D230">
-        <v>6386168.070111027</v>
+        <v>6399129.240844392</v>
       </c>
       <c r="E230">
-        <v>7779051.723380702</v>
+        <v>7801243.902902661</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4278,16 +4278,16 @@
         <v>230</v>
       </c>
       <c r="B231">
-        <v>11828026.98351098</v>
+        <v>11828484.3441002</v>
       </c>
       <c r="C231">
-        <v>21073963.2658589</v>
+        <v>21084206.19864869</v>
       </c>
       <c r="D231">
-        <v>32747333.39807696</v>
+        <v>32930955.55488706</v>
       </c>
       <c r="E231">
-        <v>45796414.76339062</v>
+        <v>46099810.51566803</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4298,13 +4298,13 @@
         <v>2299463.794828927</v>
       </c>
       <c r="C232">
-        <v>3459125.337899578</v>
+        <v>3460009.617295402</v>
       </c>
       <c r="D232">
-        <v>5856275.515548207</v>
+        <v>5880743.868555142</v>
       </c>
       <c r="E232">
-        <v>9115662.896294562</v>
+        <v>9183249.330340466</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4315,13 +4315,13 @@
         <v>2330243.354510156</v>
       </c>
       <c r="C233">
-        <v>3536616.088097135</v>
+        <v>3537460.771372813</v>
       </c>
       <c r="D233">
-        <v>5993460.553689909</v>
+        <v>6017171.004777124</v>
       </c>
       <c r="E233">
-        <v>9303004.697325423</v>
+        <v>9366691.625720982</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4332,13 +4332,13 @@
         <v>16098126.62776866</v>
       </c>
       <c r="C234">
-        <v>20568129.39128989</v>
+        <v>20569340.36519057</v>
       </c>
       <c r="D234">
-        <v>27602798.9204191</v>
+        <v>27676913.98478623</v>
       </c>
       <c r="E234">
-        <v>34566104.03382289</v>
+        <v>34738657.7657426</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -4349,13 +4349,13 @@
         <v>14383974.25536736</v>
       </c>
       <c r="C235">
-        <v>19470526.19871525</v>
+        <v>19471672.54987878</v>
       </c>
       <c r="D235">
-        <v>28250751.94672002</v>
+        <v>28326606.80133051</v>
       </c>
       <c r="E235">
-        <v>38589237.2824151</v>
+        <v>38781874.46531834</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -4366,13 +4366,13 @@
         <v>20644356.83283295</v>
       </c>
       <c r="C236">
-        <v>22906501.41025324</v>
+        <v>22907850.05868092</v>
       </c>
       <c r="D236">
-        <v>25788530.44677653</v>
+        <v>25857774.09846225</v>
       </c>
       <c r="E236">
-        <v>24959847.09330679</v>
+        <v>25084446.46267399</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4383,13 +4383,13 @@
         <v>3024782.46527627</v>
       </c>
       <c r="C237">
-        <v>4211758.456642752</v>
+        <v>4211985.945885354</v>
       </c>
       <c r="D237">
-        <v>6171984.061306933</v>
+        <v>6174614.085859847</v>
       </c>
       <c r="E237">
-        <v>8393435.199264575</v>
+        <v>8405322.814878516</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4400,13 +4400,13 @@
         <v>3168905.61787267</v>
       </c>
       <c r="C238">
-        <v>4072022.197545556</v>
+        <v>4072259.83746206</v>
       </c>
       <c r="D238">
-        <v>5888462.453877581</v>
+        <v>5891427.37625293</v>
       </c>
       <c r="E238">
-        <v>8130230.353278207</v>
+        <v>8142561.908231726</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4417,13 +4417,13 @@
         <v>4645537.432325377</v>
       </c>
       <c r="C239">
-        <v>4776908.74859526</v>
+        <v>4777141.09181475</v>
       </c>
       <c r="D239">
-        <v>5557200.273017377</v>
+        <v>5559122.035786026</v>
       </c>
       <c r="E239">
-        <v>5702077.880921704</v>
+        <v>5709546.57322517</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4434,13 +4434,13 @@
         <v>3919938.40196893</v>
       </c>
       <c r="C240">
-        <v>5518827.592225007</v>
+        <v>5519461.393534667</v>
       </c>
       <c r="D240">
-        <v>8687054.896756992</v>
+        <v>8704754.781443525</v>
       </c>
       <c r="E240">
-        <v>12670061.46312028</v>
+        <v>12741014.80058645</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -4451,13 +4451,13 @@
         <v>1028769.093793364</v>
       </c>
       <c r="C241">
-        <v>1264935.069507479</v>
+        <v>1265014.794457998</v>
       </c>
       <c r="D241">
-        <v>1563009.053728882</v>
+        <v>1564475.666766817</v>
       </c>
       <c r="E241">
-        <v>1748742.345152162</v>
+        <v>1756178.851697316</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4468,13 +4468,13 @@
         <v>3068413.245941806</v>
       </c>
       <c r="C242">
-        <v>4449467.684650013</v>
+        <v>4450041.931619187</v>
       </c>
       <c r="D242">
-        <v>7046755.019785808</v>
+        <v>7060265.519154621</v>
       </c>
       <c r="E242">
-        <v>10415043.71865264</v>
+        <v>10443119.18409187</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4485,13 +4485,13 @@
         <v>4789886.347912119</v>
       </c>
       <c r="C243">
-        <v>6519607.410705819</v>
+        <v>6521808.566812803</v>
       </c>
       <c r="D243">
-        <v>9025359.333021043</v>
+        <v>9049216.810698956</v>
       </c>
       <c r="E243">
-        <v>11732159.3254946</v>
+        <v>11764135.97623084</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4502,13 +4502,13 @@
         <v>3939691.081209232</v>
       </c>
       <c r="C244">
-        <v>4836377.918097841</v>
+        <v>4837002.099586072</v>
       </c>
       <c r="D244">
-        <v>6651609.878489408</v>
+        <v>6664362.779762774</v>
       </c>
       <c r="E244">
-        <v>8581996.024169773</v>
+        <v>8605130.207691699</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4519,13 +4519,13 @@
         <v>4009084.061143037</v>
       </c>
       <c r="C245">
-        <v>5937714.344393158</v>
+        <v>5939660.590490588</v>
       </c>
       <c r="D245">
-        <v>9553904.909459673</v>
+        <v>9577646.776178414</v>
       </c>
       <c r="E245">
-        <v>14245787.70430034</v>
+        <v>14282139.43731083</v>
       </c>
     </row>
     <row r="246" spans="1:5">
@@ -4536,13 +4536,13 @@
         <v>1130157.819648341</v>
       </c>
       <c r="C246">
-        <v>2154272.624714622</v>
+        <v>2154583.400958037</v>
       </c>
       <c r="D246">
-        <v>5072898.600955065</v>
+        <v>5083338.266534564</v>
       </c>
       <c r="E246">
-        <v>9620940.60169941</v>
+        <v>9639639.607447866</v>
       </c>
     </row>
     <row r="247" spans="1:5">
@@ -4553,13 +4553,13 @@
         <v>1130157.819648341</v>
       </c>
       <c r="C247">
-        <v>2154272.624714622</v>
+        <v>2154583.400958037</v>
       </c>
       <c r="D247">
-        <v>5072898.600955065</v>
+        <v>5083338.266534564</v>
       </c>
       <c r="E247">
-        <v>9620940.60169941</v>
+        <v>9639639.607447866</v>
       </c>
     </row>
     <row r="248" spans="1:5">
@@ -4570,13 +4570,13 @@
         <v>49426124.72269747</v>
       </c>
       <c r="C248">
-        <v>55970372.25234543</v>
+        <v>55985944.2493977</v>
       </c>
       <c r="D248">
-        <v>67676106.63453835</v>
+        <v>67797464.81504239</v>
       </c>
       <c r="E248">
-        <v>72881452.94950123</v>
+        <v>73244332.89793354</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -4587,13 +4587,13 @@
         <v>25149866.44232363</v>
       </c>
       <c r="C249">
-        <v>28264755.95420359</v>
+        <v>28267456.77134928</v>
       </c>
       <c r="D249">
-        <v>36056651.1063697</v>
+        <v>36097694.98241536</v>
       </c>
       <c r="E249">
-        <v>40070065.19284748</v>
+        <v>40248507.25060356</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4604,13 +4604,13 @@
         <v>23003169.90470337</v>
       </c>
       <c r="C250">
-        <v>29477696.62778119</v>
+        <v>29487459.52560368</v>
       </c>
       <c r="D250">
-        <v>37393931.59734645</v>
+        <v>37480573.83878274</v>
       </c>
       <c r="E250">
-        <v>44648574.67244373</v>
+        <v>44719282.37450226</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4621,13 +4621,13 @@
         <v>12649288.42253027</v>
       </c>
       <c r="C251">
-        <v>16641175.2272027</v>
+        <v>16659118.06410834</v>
       </c>
       <c r="D251">
-        <v>22847997.08370891</v>
+        <v>22905238.19758474</v>
       </c>
       <c r="E251">
-        <v>29936858.84114337</v>
+        <v>29979304.39893408</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4638,13 +4638,13 @@
         <v>5890855.852224273</v>
       </c>
       <c r="C252">
-        <v>8699964.755973358</v>
+        <v>8699971.268516004</v>
       </c>
       <c r="D252">
-        <v>14229193.70286156</v>
+        <v>14238320.79167284</v>
       </c>
       <c r="E252">
-        <v>22123919.146084</v>
+        <v>22152555.33305196</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4655,13 +4655,13 @@
         <v>712766.2274582154</v>
       </c>
       <c r="C253">
-        <v>750435.8251427779</v>
+        <v>750978.0760742299</v>
       </c>
       <c r="D253">
-        <v>895595.7896708023</v>
+        <v>897031.6394819176</v>
       </c>
       <c r="E253">
-        <v>1003153.253267354</v>
+        <v>1004400.44223055</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4672,13 +4672,13 @@
         <v>13690340.22168789</v>
       </c>
       <c r="C254">
-        <v>15355308.14238195</v>
+        <v>15365942.78357695</v>
       </c>
       <c r="D254">
-        <v>16924522.48084895</v>
+        <v>16958698.45425348</v>
       </c>
       <c r="E254">
-        <v>16789642.99214134</v>
+        <v>16809335.06538926</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4689,13 +4689,13 @@
         <v>760283.9759554298</v>
       </c>
       <c r="C255">
-        <v>808161.6578460684</v>
+        <v>808745.6203876322</v>
       </c>
       <c r="D255">
-        <v>895595.7896708023</v>
+        <v>897031.6394819176</v>
       </c>
       <c r="E255">
-        <v>820761.7526732896</v>
+        <v>821782.1800068135</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4709,10 +4709,10 @@
         <v>5250674.165650347</v>
       </c>
       <c r="D256">
-        <v>6394099.496186205</v>
+        <v>6395860.554348444</v>
       </c>
       <c r="E256">
-        <v>7346259.251731323</v>
+        <v>7352385.485580594</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4726,10 +4726,10 @@
         <v>1936015.159011155</v>
       </c>
       <c r="D257">
-        <v>2270990.220789812</v>
+        <v>2271583.458245925</v>
       </c>
       <c r="E257">
-        <v>2469856.890150546</v>
+        <v>2472690.207627088</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4743,10 +4743,10 @@
         <v>1925490.103150968</v>
       </c>
       <c r="D258">
-        <v>2712637.583052948</v>
+        <v>2714407.5405714</v>
       </c>
       <c r="E258">
-        <v>3626409.171488734</v>
+        <v>3631736.389767088</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -4760,10 +4760,10 @@
         <v>2021764.608308516</v>
       </c>
       <c r="D259">
-        <v>2648050.973932639</v>
+        <v>2649778.789605414</v>
       </c>
       <c r="E259">
-        <v>3379154.000705412</v>
+        <v>3384117.999555695</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4771,16 +4771,16 @@
         <v>259</v>
       </c>
       <c r="B260">
-        <v>6991659.309183732</v>
+        <v>6991676.729209941</v>
       </c>
       <c r="C260">
-        <v>11489350.12049105</v>
+        <v>11491646.76334421</v>
       </c>
       <c r="D260">
-        <v>23269976.75668424</v>
+        <v>23402220.65570784</v>
       </c>
       <c r="E260">
-        <v>36000030.13555083</v>
+        <v>36294724.06100957</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -4794,10 +4794,10 @@
         <v>1998167.580892851</v>
       </c>
       <c r="D261">
-        <v>4291030.654388279</v>
+        <v>4297420.002372963</v>
       </c>
       <c r="E261">
-        <v>6128900.419728744</v>
+        <v>6157940.435033605</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -4808,13 +4808,13 @@
         <v>1283217.612748265</v>
       </c>
       <c r="C262">
-        <v>2068049.731401086</v>
+        <v>2068136.710504092</v>
       </c>
       <c r="D262">
-        <v>4733572.707937378</v>
+        <v>4751090.45359046</v>
       </c>
       <c r="E262">
-        <v>8557994.532064006</v>
+        <v>8616182.79621103</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -4825,13 +4825,13 @@
         <v>1900737.532143988</v>
       </c>
       <c r="C263">
-        <v>2485691.443226941</v>
+        <v>2485791.867519895</v>
       </c>
       <c r="D263">
-        <v>4440471.270284403</v>
+        <v>4455922.403135062</v>
       </c>
       <c r="E263">
-        <v>6077099.875551198</v>
+        <v>6115742.710073553</v>
       </c>
     </row>
     <row r="264" spans="1:5">
@@ -4839,16 +4839,16 @@
         <v>263</v>
       </c>
       <c r="B264">
-        <v>854742.0298656238</v>
+        <v>854758.1037838652</v>
       </c>
       <c r="C264">
-        <v>1131760.28329044</v>
+        <v>1131778.817906616</v>
       </c>
       <c r="D264">
-        <v>2188536.544841446</v>
+        <v>2191187.584756177</v>
       </c>
       <c r="E264">
-        <v>3317352.540288046</v>
+        <v>3331798.121512719</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -4856,16 +4856,16 @@
         <v>264</v>
       </c>
       <c r="B265">
-        <v>841174.6960582329</v>
+        <v>841190.5148349151</v>
       </c>
       <c r="C265">
-        <v>1131760.28329044</v>
+        <v>1131778.817906616</v>
       </c>
       <c r="D265">
-        <v>2188536.544841446</v>
+        <v>2191187.584756177</v>
       </c>
       <c r="E265">
-        <v>3382398.668528988</v>
+        <v>3397127.496444341</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -4876,13 +4876,13 @@
         <v>674165.1257108432</v>
       </c>
       <c r="C266">
-        <v>1217856.563912126</v>
+        <v>1219602.000351511</v>
       </c>
       <c r="D266">
-        <v>2572928.728864162</v>
+        <v>2597742.33935793</v>
       </c>
       <c r="E266">
-        <v>4388932.415995009</v>
+        <v>4425949.083165607</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -4890,16 +4890,16 @@
         <v>266</v>
       </c>
       <c r="B267">
-        <v>990415.3679395324</v>
+        <v>990433.9932733676</v>
       </c>
       <c r="C267">
-        <v>1248838.933286003</v>
+        <v>1248859.385276266</v>
       </c>
       <c r="D267">
-        <v>2107479.635773244</v>
+        <v>2110032.489024467</v>
       </c>
       <c r="E267">
-        <v>2536799.001396741</v>
+        <v>2547845.622333256</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -4913,10 +4913,10 @@
         <v>1873282.107087048</v>
       </c>
       <c r="D268">
-        <v>4565656.616269128</v>
+        <v>4572454.882524833</v>
       </c>
       <c r="E268">
-        <v>7720057.259466014</v>
+        <v>7756636.509513483</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -4930,10 +4930,10 @@
         <v>1998167.580892851</v>
       </c>
       <c r="D269">
-        <v>4325358.899623385</v>
+        <v>4331799.362391948</v>
       </c>
       <c r="E269">
-        <v>6246763.889338912</v>
+        <v>6276362.366476559</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -4944,13 +4944,13 @@
         <v>963285.6929105881</v>
       </c>
       <c r="C270">
-        <v>1671206.057437898</v>
+        <v>1671775.277032734</v>
       </c>
       <c r="D270">
-        <v>3903393.213151759</v>
+        <v>3916225.04409183</v>
       </c>
       <c r="E270">
-        <v>6453037.743633714</v>
+        <v>6496697.502675327</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -4961,13 +4961,13 @@
         <v>318723.4841730336</v>
       </c>
       <c r="C271">
-        <v>474054.9977037287</v>
+        <v>474109.9428007086</v>
       </c>
       <c r="D271">
-        <v>929179.6627941318</v>
+        <v>930413.911260728</v>
       </c>
       <c r="E271">
-        <v>1141103.596391476</v>
+        <v>1145191.913142147</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -4978,13 +4978,13 @@
         <v>229777.3955666056</v>
       </c>
       <c r="C272">
-        <v>397181.2142923133</v>
+        <v>397227.2493735667</v>
       </c>
       <c r="D272">
-        <v>1025301.696876283</v>
+        <v>1026663.626218734</v>
       </c>
       <c r="E272">
-        <v>1793162.794329462</v>
+        <v>1799587.292080517</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -4995,13 +4995,13 @@
         <v>782454.5994378782</v>
       </c>
       <c r="C273">
-        <v>1261249.334446328</v>
+        <v>1262183.102842188</v>
       </c>
       <c r="D273">
-        <v>2729208.432471722</v>
+        <v>2743082.270303953</v>
       </c>
       <c r="E273">
-        <v>4227731.772620193</v>
+        <v>4261231.903476015</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5012,13 +5012,13 @@
         <v>947761.909178275</v>
       </c>
       <c r="C274">
-        <v>1374197.036038537</v>
+        <v>1375214.425484772</v>
       </c>
       <c r="D274">
-        <v>2603244.966357642</v>
+        <v>2616478.473213002</v>
       </c>
       <c r="E274">
-        <v>3221128.969615385</v>
+        <v>3246652.878838868</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5029,13 +5029,13 @@
         <v>2025062.677372875</v>
       </c>
       <c r="C275">
-        <v>3201855.137659169</v>
+        <v>3201855.285595709</v>
       </c>
       <c r="D275">
-        <v>6276761.357410326</v>
+        <v>6278619.6773305</v>
       </c>
       <c r="E275">
-        <v>9515854.414202662</v>
+        <v>9519379.3661188</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5049,10 +5049,10 @@
         <v>689802.6298062593</v>
       </c>
       <c r="D276">
-        <v>1561087.592451404</v>
+        <v>1561905.284520157</v>
       </c>
       <c r="E276">
-        <v>2389521.865949195</v>
+        <v>2391538.766300355</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5063,13 +5063,13 @@
         <v>3507098.25493696</v>
       </c>
       <c r="C277">
-        <v>4390207.049113479</v>
+        <v>4390232.353731168</v>
       </c>
       <c r="D277">
-        <v>6505846.1391591</v>
+        <v>6510978.080987195</v>
       </c>
       <c r="E277">
-        <v>7640671.853847832</v>
+        <v>7644303.742176668</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5080,13 +5080,13 @@
         <v>2443462.504954366</v>
       </c>
       <c r="C278">
-        <v>3358193.418037713</v>
+        <v>3358767.548310053</v>
       </c>
       <c r="D278">
-        <v>5129485.946347797</v>
+        <v>5134556.705530118</v>
       </c>
       <c r="E278">
-        <v>6863387.918014932</v>
+        <v>6867956.5294329</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5100,10 +5100,10 @@
         <v>1267783.455396609</v>
       </c>
       <c r="D279">
-        <v>1584666.807598485</v>
+        <v>1585431.088866344</v>
       </c>
       <c r="E279">
-        <v>1801423.185607145</v>
+        <v>1802319.251887601</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5117,10 +5117,10 @@
         <v>1267783.455396609</v>
       </c>
       <c r="D280">
-        <v>1584666.807598485</v>
+        <v>1585431.088866344</v>
       </c>
       <c r="E280">
-        <v>1801423.185607145</v>
+        <v>1802319.251887601</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5131,13 +5131,13 @@
         <v>2517270.104362735</v>
       </c>
       <c r="C281">
-        <v>3705623.891978217</v>
+        <v>3705711.305755411</v>
       </c>
       <c r="D281">
-        <v>7287665.179107976</v>
+        <v>7294133.874931929</v>
       </c>
       <c r="E281">
-        <v>9716081.34342852</v>
+        <v>9730658.67189605</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5148,13 +5148,13 @@
         <v>879574.634274257</v>
       </c>
       <c r="C282">
-        <v>1199508.571965387</v>
+        <v>1199825.541503911</v>
       </c>
       <c r="D282">
-        <v>2168323.193257165</v>
+        <v>2169519.713899788</v>
       </c>
       <c r="E282">
-        <v>2315235.526411992</v>
+        <v>2317619.235074366</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5165,13 +5165,13 @@
         <v>839593.9690799726</v>
       </c>
       <c r="C283">
-        <v>1172553.323157176</v>
+        <v>1172863.169784722</v>
       </c>
       <c r="D283">
-        <v>2231173.140887808</v>
+        <v>2232404.343288187</v>
       </c>
       <c r="E283">
-        <v>2610797.50850714</v>
+        <v>2613485.520403009</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5182,13 +5182,13 @@
         <v>687667.4413416919</v>
       </c>
       <c r="C284">
-        <v>1091687.576732543</v>
+        <v>1091976.054627155</v>
       </c>
       <c r="D284">
-        <v>2356873.036149092</v>
+        <v>2358173.602064986</v>
       </c>
       <c r="E284">
-        <v>3349702.463745011</v>
+        <v>3353151.233724616</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5202,10 +5202,10 @@
         <v>760190.6532558776</v>
       </c>
       <c r="D285">
-        <v>1401792.940160445</v>
+        <v>1402527.194262998</v>
       </c>
       <c r="E285">
-        <v>1593014.577299463</v>
+        <v>1594359.17753357</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5219,10 +5219,10 @@
         <v>1307401.688377753</v>
       </c>
       <c r="D286">
-        <v>1584666.807598485</v>
+        <v>1585431.088866344</v>
       </c>
       <c r="E286">
-        <v>1576245.287406252</v>
+        <v>1577029.345401651</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5230,16 +5230,16 @@
         <v>286</v>
       </c>
       <c r="B287">
-        <v>7925961.619514151</v>
+        <v>7925964.146473891</v>
       </c>
       <c r="C287">
-        <v>10899159.95328041</v>
+        <v>10904236.91034509</v>
       </c>
       <c r="D287">
-        <v>16107024.24038518</v>
+        <v>16144691.17317506</v>
       </c>
       <c r="E287">
-        <v>21825394.12348301</v>
+        <v>21862169.53875788</v>
       </c>
     </row>
     <row r="288" spans="1:5">
@@ -5247,16 +5247,16 @@
         <v>287</v>
       </c>
       <c r="B288">
-        <v>3365098.057658988</v>
+        <v>3365098.61697187</v>
       </c>
       <c r="C288">
-        <v>5051252.088373665</v>
+        <v>5054423.888989954</v>
       </c>
       <c r="D288">
-        <v>8836028.358921811</v>
+        <v>8865413.144672466</v>
       </c>
       <c r="E288">
-        <v>13782848.38720663</v>
+        <v>13817550.38954076</v>
       </c>
     </row>
     <row r="289" spans="1:5">
@@ -5267,13 +5267,13 @@
         <v>107111088.4806539</v>
       </c>
       <c r="C289">
-        <v>118723099.1987315</v>
+        <v>118912145.1633818</v>
       </c>
       <c r="D289">
-        <v>151162791.2933905</v>
+        <v>151865919.4988784</v>
       </c>
       <c r="E289">
-        <v>176114133.0030767</v>
+        <v>176573859.5688852</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5281,16 +5281,16 @@
         <v>289</v>
       </c>
       <c r="B290">
-        <v>6574530.375633857</v>
+        <v>6574532.471729495</v>
       </c>
       <c r="C290">
-        <v>9678092.240672234</v>
+        <v>9682600.410015969</v>
       </c>
       <c r="D290">
-        <v>16558020.91911596</v>
+        <v>16596742.52602396</v>
       </c>
       <c r="E290">
-        <v>26276062.72905602</v>
+        <v>26320337.44470066</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5301,13 +5301,13 @@
         <v>5591430.347010169</v>
       </c>
       <c r="C291">
-        <v>6287361.908382677</v>
+        <v>6290660.155390495</v>
       </c>
       <c r="D291">
-        <v>8471501.211425396</v>
+        <v>8492587.937068755</v>
       </c>
       <c r="E291">
-        <v>9613126.279959135</v>
+        <v>9634165.885937918</v>
       </c>
     </row>
     <row r="292" spans="1:5">
@@ -5318,13 +5318,13 @@
         <v>856288.234643636</v>
       </c>
       <c r="C292">
-        <v>1094155.443859294</v>
+        <v>1094188.410923022</v>
       </c>
       <c r="D292">
-        <v>1603066.181117988</v>
+        <v>1605748.4484927</v>
       </c>
       <c r="E292">
-        <v>2064623.247144507</v>
+        <v>2068834.281574172</v>
       </c>
     </row>
     <row r="293" spans="1:5">
@@ -5335,13 +5335,13 @@
         <v>3842321.952316632</v>
       </c>
       <c r="C293">
-        <v>5208404.524677025</v>
+        <v>5208635.164479135</v>
       </c>
       <c r="D293">
-        <v>8114470.197232502</v>
+        <v>8125867.024581582</v>
       </c>
       <c r="E293">
-        <v>11640088.91427495</v>
+        <v>11659924.54536632</v>
       </c>
     </row>
     <row r="294" spans="1:5">
@@ -5352,13 +5352,13 @@
         <v>1110003.267130639</v>
       </c>
       <c r="C294">
-        <v>1215728.270954771</v>
+        <v>1215764.90102558</v>
       </c>
       <c r="D294">
-        <v>1484320.538072211</v>
+        <v>1486804.118974722</v>
       </c>
       <c r="E294">
-        <v>1508763.142144063</v>
+        <v>1511840.436534972</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5369,13 +5369,13 @@
         <v>9057512.996127551</v>
       </c>
       <c r="C295">
-        <v>12015448.75263101</v>
+        <v>12016857.83340616</v>
       </c>
       <c r="D295">
-        <v>19036775.30631714</v>
+        <v>19051116.87215975</v>
       </c>
       <c r="E295">
-        <v>26493371.5640037</v>
+        <v>26530404.49744667</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5386,13 +5386,13 @@
         <v>3901807.880064477</v>
       </c>
       <c r="C296">
-        <v>5008752.701287904</v>
+        <v>5009761.343663894</v>
       </c>
       <c r="D296">
-        <v>7869065.483321466</v>
+        <v>7878258.702823802</v>
       </c>
       <c r="E296">
-        <v>11031572.16470196</v>
+        <v>11050466.47518993</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5403,13 +5403,13 @@
         <v>2336363.908148434</v>
       </c>
       <c r="C297">
-        <v>3789587.453766215</v>
+        <v>3790683.888801067</v>
       </c>
       <c r="D297">
-        <v>8605920.420915704</v>
+        <v>8622717.176806051</v>
       </c>
       <c r="E297">
-        <v>16397064.61954664</v>
+        <v>16431215.90899859</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5420,13 +5420,13 @@
         <v>9076346.760663921</v>
       </c>
       <c r="C298">
-        <v>13592218.66387956</v>
+        <v>13594635.83226412</v>
       </c>
       <c r="D298">
-        <v>23486253.24707557</v>
+        <v>23506547.64851882</v>
       </c>
       <c r="E298">
-        <v>35308667.63590363</v>
+        <v>35367743.96980448</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5437,13 +5437,13 @@
         <v>10090212.03074095</v>
       </c>
       <c r="C299">
-        <v>16558340.93032857</v>
+        <v>16561378.58574475</v>
       </c>
       <c r="D299">
-        <v>30085868.76623288</v>
+        <v>30116040.07626076</v>
       </c>
       <c r="E299">
-        <v>46466342.66016971</v>
+        <v>46547823.09895441</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5454,13 +5454,13 @@
         <v>10521901.32484278</v>
       </c>
       <c r="C300">
-        <v>12665857.65946859</v>
+        <v>12667343.01527145</v>
       </c>
       <c r="D300">
-        <v>18281775.71909776</v>
+        <v>18295548.4976265</v>
       </c>
       <c r="E300">
-        <v>22784299.54504318</v>
+        <v>22816147.86780414</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5471,13 +5471,13 @@
         <v>3718329.106515646</v>
       </c>
       <c r="C301">
-        <v>4972937.090277688</v>
+        <v>4973915.419506809</v>
       </c>
       <c r="D301">
-        <v>8115049.191819247</v>
+        <v>8123954.261493122</v>
       </c>
       <c r="E301">
-        <v>11724995.48898333</v>
+        <v>11743876.49256575</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5488,13 +5488,13 @@
         <v>13676743.6883615</v>
       </c>
       <c r="C302">
-        <v>15950357.2202848</v>
+        <v>15952697.33432008</v>
       </c>
       <c r="D302">
-        <v>22318055.50060039</v>
+        <v>22334279.16745879</v>
       </c>
       <c r="E302">
-        <v>26184251.14865058</v>
+        <v>26222184.65333976</v>
       </c>
     </row>
     <row r="303" spans="1:5">
@@ -5505,13 +5505,13 @@
         <v>13676743.6883615</v>
       </c>
       <c r="C303">
-        <v>15950357.2202848</v>
+        <v>15952697.33432008</v>
       </c>
       <c r="D303">
-        <v>22318055.50060039</v>
+        <v>22334279.16745879</v>
       </c>
       <c r="E303">
-        <v>26184251.14865058</v>
+        <v>26222184.65333976</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5522,13 +5522,13 @@
         <v>1726015.505080107</v>
       </c>
       <c r="C304">
-        <v>2252551.504369035</v>
+        <v>2252787.824699438</v>
       </c>
       <c r="D304">
-        <v>3460739.180789764</v>
+        <v>3465598.265704055</v>
       </c>
       <c r="E304">
-        <v>4436990.786602303</v>
+        <v>4449270.439652805</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5539,13 +5539,13 @@
         <v>1390401.379092308</v>
       </c>
       <c r="C305">
-        <v>1970982.566322906</v>
+        <v>1971189.346612009</v>
       </c>
       <c r="D305">
-        <v>3615697.651571395</v>
+        <v>3620774.307451998</v>
       </c>
       <c r="E305">
-        <v>5768088.022582995</v>
+        <v>5784051.571548647</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5556,13 +5556,13 @@
         <v>558709.5861274074</v>
       </c>
       <c r="C306">
-        <v>741107.5451189398</v>
+        <v>741181.6962239001</v>
       </c>
       <c r="D306">
-        <v>1326908.34025555</v>
+        <v>1327608.432242773</v>
       </c>
       <c r="E306">
-        <v>2042258.804860848</v>
+        <v>2046212.252867331</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5573,13 +5573,13 @@
         <v>1558208.442086208</v>
       </c>
       <c r="C307">
-        <v>2127409.754126311</v>
+        <v>2127632.945549469</v>
       </c>
       <c r="D307">
-        <v>3512392.004383641</v>
+        <v>3517323.61295337</v>
       </c>
       <c r="E307">
-        <v>5102539.404592649</v>
+        <v>5116661.005600726</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5590,13 +5590,13 @@
         <v>410572.3575938847</v>
       </c>
       <c r="C308">
-        <v>693389.4994940229</v>
+        <v>693444.3915297397</v>
       </c>
       <c r="D308">
-        <v>1410886.527445979</v>
+        <v>1411561.782246315</v>
       </c>
       <c r="E308">
-        <v>2449826.220466018</v>
+        <v>2454347.5213456</v>
       </c>
     </row>
     <row r="309" spans="1:5">
@@ -5607,13 +5607,13 @@
         <v>533313.6958488888</v>
       </c>
       <c r="C309">
-        <v>741107.5451189398</v>
+        <v>741181.6962239001</v>
       </c>
       <c r="D309">
-        <v>1326908.34025555</v>
+        <v>1327608.432242773</v>
       </c>
       <c r="E309">
-        <v>2112681.522269843</v>
+        <v>2116771.296069653</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5624,13 +5624,13 @@
         <v>1873019.715350718</v>
       </c>
       <c r="C310">
-        <v>2214242.089534825</v>
+        <v>2214447.443983453</v>
       </c>
       <c r="D310">
-        <v>3446778.16858157</v>
+        <v>3451332.239823495</v>
       </c>
       <c r="E310">
-        <v>4610761.553186037</v>
+        <v>4622906.353316562</v>
       </c>
     </row>
     <row r="311" spans="1:5">
@@ -5641,13 +5641,13 @@
         <v>391136.6495756651</v>
       </c>
       <c r="C311">
-        <v>503766.1442897963</v>
+        <v>503769.1944706237</v>
       </c>
       <c r="D311">
-        <v>971213.2431720974</v>
+        <v>971988.1497853335</v>
       </c>
       <c r="E311">
-        <v>1416155.681628357</v>
+        <v>1421243.794904147</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -5658,13 +5658,13 @@
         <v>456326.0911716093</v>
       </c>
       <c r="C312">
-        <v>535251.5283079086</v>
+        <v>535254.7691250377</v>
       </c>
       <c r="D312">
-        <v>937723.1313385768</v>
+        <v>938471.3170341151</v>
       </c>
       <c r="E312">
-        <v>1143818.050545981</v>
+        <v>1147927.680499504</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5675,13 +5675,13 @@
         <v>445461.1842389519</v>
       </c>
       <c r="C313">
-        <v>535251.5283079086</v>
+        <v>535254.7691250377</v>
       </c>
       <c r="D313">
-        <v>937723.1313385768</v>
+        <v>938471.3170341151</v>
       </c>
       <c r="E313">
-        <v>1143818.050545981</v>
+        <v>1147927.680499504</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -5692,13 +5692,13 @@
         <v>369406.8357103504</v>
       </c>
       <c r="C314">
-        <v>503766.1442897963</v>
+        <v>503769.1944706237</v>
       </c>
       <c r="D314">
-        <v>1004703.355005618</v>
+        <v>1005504.982536552</v>
       </c>
       <c r="E314">
-        <v>1525090.734061308</v>
+        <v>1530570.240666005</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -5709,13 +5709,13 @@
         <v>23651503.50256756</v>
       </c>
       <c r="C315">
-        <v>27507091.16265202</v>
+        <v>27533278.61172457</v>
       </c>
       <c r="D315">
-        <v>36585046.94969819</v>
+        <v>36709722.89524806</v>
       </c>
       <c r="E315">
-        <v>45005745.10598723</v>
+        <v>45081792.3047455</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -5726,13 +5726,13 @@
         <v>40444303.98543089</v>
       </c>
       <c r="C316">
-        <v>46447811.24959395</v>
+        <v>46462682.11134295</v>
       </c>
       <c r="D316">
-        <v>60696523.12255114</v>
+        <v>60780078.07997801</v>
       </c>
       <c r="E316">
-        <v>76543290.53312589</v>
+        <v>76603611.47039032</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -5743,13 +5743,13 @@
         <v>11412026.02204918</v>
       </c>
       <c r="C317">
-        <v>14201850.20066497</v>
+        <v>14208862.94138901</v>
       </c>
       <c r="D317">
-        <v>19835161.67204729</v>
+        <v>19874355.11108964</v>
       </c>
       <c r="E317">
-        <v>26862663.35875436</v>
+        <v>26890705.04515094</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -5760,13 +5760,13 @@
         <v>5608960.070449245</v>
       </c>
       <c r="C318">
-        <v>7335726.612811438</v>
+        <v>7341536.052997435</v>
       </c>
       <c r="D318">
-        <v>10370489.738499</v>
+        <v>10400551.60415276</v>
       </c>
       <c r="E318">
-        <v>13813968.8540653</v>
+        <v>13833187.75903982</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -5777,13 +5777,13 @@
         <v>3976102.605599559</v>
       </c>
       <c r="C319">
-        <v>5142943.992378453</v>
+        <v>5148293.398981983</v>
       </c>
       <c r="D319">
-        <v>7314254.382184266</v>
+        <v>7343431.535604659</v>
       </c>
       <c r="E319">
-        <v>9590226.02055536</v>
+        <v>9609707.978843119</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -5794,13 +5794,13 @@
         <v>4026711.145678888</v>
       </c>
       <c r="C320">
-        <v>5079486.238279235</v>
+        <v>5083818.381028392</v>
       </c>
       <c r="D320">
-        <v>6963531.983486957</v>
+        <v>6987590.0956878</v>
       </c>
       <c r="E320">
-        <v>8948656.843593618</v>
+        <v>8965144.358450873</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -5811,13 +5811,13 @@
         <v>19007989.37728764</v>
       </c>
       <c r="C321">
-        <v>24007341.97988788</v>
+        <v>24027333.38419235</v>
       </c>
       <c r="D321">
-        <v>32410927.64736387</v>
+        <v>32496379.72692524</v>
       </c>
       <c r="E321">
-        <v>41249523.63256838</v>
+        <v>41302989.63552908</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -5828,13 +5828,13 @@
         <v>12514400.28643478</v>
       </c>
       <c r="C322">
-        <v>13549334.26223471</v>
+        <v>13559408.09155725</v>
       </c>
       <c r="D322">
-        <v>16901242.48615656</v>
+        <v>16950170.30895135</v>
       </c>
       <c r="E322">
-        <v>18912237.37683032</v>
+        <v>18944053.20631511</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -5845,13 +5845,13 @@
         <v>3233496.335054009</v>
       </c>
       <c r="C323">
-        <v>4370840.315249691</v>
+        <v>4370928.492602196</v>
       </c>
       <c r="D323">
-        <v>6696675.189028784</v>
+        <v>6709878.393395379</v>
       </c>
       <c r="E323">
-        <v>9742251.004349338</v>
+        <v>9753739.923707817</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -5862,13 +5862,13 @@
         <v>3560939.001894922</v>
       </c>
       <c r="C324">
-        <v>4516534.992424681</v>
+        <v>4516626.109022269</v>
       </c>
       <c r="D324">
-        <v>6564067.759543065</v>
+        <v>6577009.514318244</v>
       </c>
       <c r="E324">
-        <v>9052534.11908567</v>
+        <v>9063209.663622309</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -5879,13 +5879,13 @@
         <v>2987914.334923325</v>
       </c>
       <c r="C325">
-        <v>4176580.745683038</v>
+        <v>4176665.004042098</v>
       </c>
       <c r="D325">
-        <v>6762978.903771643</v>
+        <v>6776312.832933947</v>
       </c>
       <c r="E325">
-        <v>10431967.88961301</v>
+        <v>10444270.18379333</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -5896,13 +5896,13 @@
         <v>6581825.585575202</v>
       </c>
       <c r="C326">
-        <v>9728711.17219469</v>
+        <v>9729854.977947794</v>
       </c>
       <c r="D326">
-        <v>14960502.84106425</v>
+        <v>14983097.93272252</v>
       </c>
       <c r="E326">
-        <v>21880640.53362342</v>
+        <v>21898379.96988806</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -5913,13 +5913,13 @@
         <v>3195015.515884956</v>
       </c>
       <c r="C327">
-        <v>4922801.300445161</v>
+        <v>4924864.403202959</v>
       </c>
       <c r="D327">
-        <v>7769508.653845054</v>
+        <v>7806961.988071435</v>
       </c>
       <c r="E327">
-        <v>11129132.34389176</v>
+        <v>11161041.78639017</v>
       </c>
     </row>
     <row r="328" spans="1:5">
@@ -5930,13 +5930,13 @@
         <v>3646485.099651309</v>
       </c>
       <c r="C328">
-        <v>4922801.300445161</v>
+        <v>4924864.403202959</v>
       </c>
       <c r="D328">
-        <v>7514770.665194396</v>
+        <v>7550996.021249421</v>
       </c>
       <c r="E328">
-        <v>10623262.69189668</v>
+        <v>10653721.70519062</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -5947,13 +5947,13 @@
         <v>32531.18562179777</v>
       </c>
       <c r="C329">
-        <v>41467.9477852537</v>
+        <v>41475.71467232031</v>
       </c>
       <c r="D329">
-        <v>61612.81792198597</v>
+        <v>61808.55711503122</v>
       </c>
       <c r="E329">
-        <v>82766.19747395533</v>
+        <v>82952.64290947732</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -5964,13 +5964,13 @@
         <v>4896708.562388901</v>
       </c>
       <c r="C330">
-        <v>5494197.879961117</v>
+        <v>5496500.450003303</v>
       </c>
       <c r="D330">
-        <v>6941610.190730417</v>
+        <v>6975072.595899889</v>
       </c>
       <c r="E330">
-        <v>7756667.997257895</v>
+        <v>7778907.911726482</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -5981,13 +5981,13 @@
         <v>4173903.372681057</v>
       </c>
       <c r="C331">
-        <v>5114672.972161851</v>
+        <v>5116886.666985453</v>
       </c>
       <c r="D331">
-        <v>7177693.866663623</v>
+        <v>7214150.14759523</v>
       </c>
       <c r="E331">
-        <v>9049658.735380903</v>
+        <v>9077596.288944632</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -5998,13 +5998,13 @@
         <v>9032194.683345087</v>
       </c>
       <c r="C332">
-        <v>11544994.59081646</v>
+        <v>11547727.3605762</v>
       </c>
       <c r="D332">
-        <v>17175136.1174982</v>
+        <v>17230735.44581671</v>
       </c>
       <c r="E332">
-        <v>23556674.74069201</v>
+        <v>23601343.46824177</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -6015,13 +6015,13 @@
         <v>7506939.862401135</v>
       </c>
       <c r="C333">
-        <v>10151746.2573773</v>
+        <v>10153899.68521159</v>
       </c>
       <c r="D333">
-        <v>15094314.76948486</v>
+        <v>15125508.27537198</v>
       </c>
       <c r="E333">
-        <v>20608890.56009744</v>
+        <v>20634133.03087991</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6032,13 +6032,13 @@
         <v>15462182.10064872</v>
       </c>
       <c r="C334">
-        <v>19717249.58646623</v>
+        <v>19723582.14391522</v>
       </c>
       <c r="D334">
-        <v>27977757.27489799</v>
+        <v>28044056.2380839</v>
       </c>
       <c r="E334">
-        <v>36457505.28742202</v>
+        <v>36502637.10691589</v>
       </c>
     </row>
     <row r="335" spans="1:5">
@@ -6049,13 +6049,13 @@
         <v>6491529.667312783</v>
       </c>
       <c r="C335">
-        <v>9347514.543306679</v>
+        <v>9351315.733021136</v>
       </c>
       <c r="D335">
-        <v>15922359.03763371</v>
+        <v>15961697.87513311</v>
       </c>
       <c r="E335">
-        <v>24266088.97692312</v>
+        <v>24296418.07153197</v>
       </c>
     </row>
     <row r="336" spans="1:5">
@@ -6066,13 +6066,13 @@
         <v>6285028.360275378</v>
       </c>
       <c r="C336">
-        <v>7076828.53121121</v>
+        <v>7077666.032540501</v>
       </c>
       <c r="D336">
-        <v>9497433.426679285</v>
+        <v>9530102.348228535</v>
       </c>
       <c r="E336">
-        <v>11680602.92767471</v>
+        <v>11706342.56924438</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6083,13 +6083,13 @@
         <v>5654751.437125012</v>
       </c>
       <c r="C337">
-        <v>8216857.580106679</v>
+        <v>8216875.461490048</v>
       </c>
       <c r="D337">
-        <v>12866149.55459855</v>
+        <v>12877120.69487433</v>
       </c>
       <c r="E337">
-        <v>17369551.37781625</v>
+        <v>17373966.68636722</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6100,13 +6100,13 @@
         <v>4844907.287095912</v>
       </c>
       <c r="C338">
-        <v>7718647.696885258</v>
+        <v>7718647.998858496</v>
       </c>
       <c r="D338">
-        <v>13937645.9053502</v>
+        <v>13941170.02925688</v>
       </c>
       <c r="E338">
-        <v>21561265.11203083</v>
+        <v>21564055.72152687</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6117,13 +6117,13 @@
         <v>5725435.830089075</v>
       </c>
       <c r="C339">
-        <v>8143053.470105721</v>
+        <v>8143071.190877861</v>
       </c>
       <c r="D339">
-        <v>12828196.31107466</v>
+        <v>12839135.08810478</v>
       </c>
       <c r="E339">
-        <v>17420191.46929677</v>
+        <v>17424619.65046742</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6137,10 +6137,10 @@
         <v>3558224.906871082</v>
       </c>
       <c r="D340">
-        <v>5114011.524004397</v>
+        <v>5115301.034553332</v>
       </c>
       <c r="E340">
-        <v>6006427.545234904</v>
+        <v>6007551.878402606</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6154,10 +6154,10 @@
         <v>3145991.533514067</v>
       </c>
       <c r="D341">
-        <v>5607778.153908269</v>
+        <v>5609192.168923999</v>
       </c>
       <c r="E341">
-        <v>8342260.479492922</v>
+        <v>8343822.053336952</v>
       </c>
     </row>
     <row r="342" spans="1:5">
@@ -6168,13 +6168,13 @@
         <v>643222.221296162</v>
       </c>
       <c r="C342">
-        <v>803418.1276290106</v>
+        <v>803635.0151179426</v>
       </c>
       <c r="D342">
-        <v>1113112.472602944</v>
+        <v>1113610.158689776</v>
       </c>
       <c r="E342">
-        <v>1177070.510586685</v>
+        <v>1177321.464489947</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6185,13 +6185,13 @@
         <v>625837.8369368062</v>
       </c>
       <c r="C343">
-        <v>778311.311140604</v>
+        <v>778521.4208955069</v>
       </c>
       <c r="D343">
-        <v>1113112.472602944</v>
+        <v>1113610.158689776</v>
       </c>
       <c r="E343">
-        <v>1284076.920640019</v>
+        <v>1284350.688534488</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6205,10 +6205,10 @@
         <v>3710100.36021314</v>
       </c>
       <c r="D344">
-        <v>4972935.344031862</v>
+        <v>4974189.281875999</v>
       </c>
       <c r="E344">
-        <v>5243706.587109837</v>
+        <v>5244688.147811798</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6222,10 +6222,10 @@
         <v>1078794.260730894</v>
       </c>
       <c r="D345">
-        <v>1713077.303666163</v>
+        <v>1713339.32555421</v>
       </c>
       <c r="E345">
-        <v>1996887.538307087</v>
+        <v>1997331.195473748</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6239,10 +6239,10 @@
         <v>1062692.853854314</v>
       </c>
       <c r="D346">
-        <v>1683541.488085712</v>
+        <v>1683798.992355</v>
       </c>
       <c r="E346">
-        <v>1955285.714592356</v>
+        <v>1955720.128901379</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6256,10 +6256,10 @@
         <v>1062692.853854314</v>
       </c>
       <c r="D347">
-        <v>1683541.488085712</v>
+        <v>1683798.992355</v>
       </c>
       <c r="E347">
-        <v>1955285.714592356</v>
+        <v>1955720.128901379</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6270,13 +6270,13 @@
         <v>751828.8662512826</v>
       </c>
       <c r="C348">
-        <v>968926.0244577753</v>
+        <v>968932.9764775683</v>
       </c>
       <c r="D348">
-        <v>1410502.966066428</v>
+        <v>1411054.252960977</v>
       </c>
       <c r="E348">
-        <v>1705294.320744895</v>
+        <v>1705685.990444632</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6287,13 +6287,13 @@
         <v>883398.9178452571</v>
       </c>
       <c r="C349">
-        <v>1045420.184283389</v>
+        <v>1045427.68514685</v>
       </c>
       <c r="D349">
-        <v>1334259.562495269</v>
+        <v>1334781.050098222</v>
       </c>
       <c r="E349">
-        <v>1404360.028848737</v>
+        <v>1404682.580366168</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6304,13 +6304,13 @@
         <v>883398.9178452571</v>
       </c>
       <c r="C350">
-        <v>1045420.184283389</v>
+        <v>1045427.68514685</v>
       </c>
       <c r="D350">
-        <v>1334259.562495269</v>
+        <v>1334781.050098222</v>
       </c>
       <c r="E350">
-        <v>1404360.028848737</v>
+        <v>1404682.580366168</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6321,13 +6321,13 @@
         <v>918961.2862263727</v>
       </c>
       <c r="C351">
-        <v>1428969.721904981</v>
+        <v>1429103.730515687</v>
       </c>
       <c r="D351">
-        <v>2607767.886247294</v>
+        <v>2608690.01784438</v>
       </c>
       <c r="E351">
-        <v>3318666.202913474</v>
+        <v>3319995.584001334</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6338,13 +6338,13 @@
         <v>1099471.538877982</v>
       </c>
       <c r="C352">
-        <v>1525150.37626397</v>
+        <v>1525293.404685013</v>
       </c>
       <c r="D352">
-        <v>2471946.642171914</v>
+        <v>2472820.746081652</v>
       </c>
       <c r="E352">
-        <v>2593900.020668002</v>
+        <v>2594939.077150468</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -6355,13 +6355,13 @@
         <v>4809822.649762095</v>
       </c>
       <c r="C353">
-        <v>6424808.979644515</v>
+        <v>6425484.323714484</v>
       </c>
       <c r="D353">
-        <v>9265607.358261591</v>
+        <v>9270730.497550549</v>
       </c>
       <c r="E353">
-        <v>12244972.75621838</v>
+        <v>12272660.44267857</v>
       </c>
     </row>
     <row r="354" spans="1:5">
@@ -6372,13 +6372,13 @@
         <v>6598118.550570394</v>
       </c>
       <c r="C354">
-        <v>7105001.281631107</v>
+        <v>7105075.269773681</v>
       </c>
       <c r="D354">
-        <v>8365057.408321769</v>
+        <v>8365968.886018399</v>
       </c>
       <c r="E354">
-        <v>8602860.10201453</v>
+        <v>8609091.448283102</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6389,13 +6389,13 @@
         <v>6389167.400430245</v>
       </c>
       <c r="C355">
-        <v>7042579.073841102</v>
+        <v>7043319.354840877</v>
       </c>
       <c r="D355">
-        <v>8508322.141480595</v>
+        <v>8513026.562654592</v>
       </c>
       <c r="E355">
-        <v>8943632.062139895</v>
+        <v>8963854.93117209</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6406,13 +6406,13 @@
         <v>1210530.441346945</v>
       </c>
       <c r="C356">
-        <v>1547314.292161064</v>
+        <v>1547337.720918732</v>
       </c>
       <c r="D356">
-        <v>2146201.693398425</v>
+        <v>2146313.916199628</v>
       </c>
       <c r="E356">
-        <v>2568329.699652463</v>
+        <v>2569605.85954173</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6423,13 +6423,13 @@
         <v>1406351.542153069</v>
       </c>
       <c r="C357">
-        <v>1644021.43542113</v>
+        <v>1644046.328476153</v>
       </c>
       <c r="D357">
-        <v>2037072.793734099</v>
+        <v>2037179.310291173</v>
       </c>
       <c r="E357">
-        <v>2083739.190284073</v>
+        <v>2084774.565288574</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6440,13 +6440,13 @@
         <v>1388549.623897967</v>
       </c>
       <c r="C358">
-        <v>1644021.43542113</v>
+        <v>1644046.328476153</v>
       </c>
       <c r="D358">
-        <v>2037072.793734099</v>
+        <v>2037179.310291173</v>
       </c>
       <c r="E358">
-        <v>2132198.241220912</v>
+        <v>2133257.69471389</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -6457,13 +6457,13 @@
         <v>479810.4706366011</v>
       </c>
       <c r="C359">
-        <v>764188.9396892715</v>
+        <v>764218.6369744964</v>
       </c>
       <c r="D359">
-        <v>1392465.875621618</v>
+        <v>1392824.815897092</v>
       </c>
       <c r="E359">
-        <v>1810650.563407565</v>
+        <v>1811065.262773952</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6474,13 +6474,13 @@
         <v>627444.4616017091</v>
       </c>
       <c r="C360">
-        <v>824125.327115881</v>
+        <v>824157.3535999471</v>
       </c>
       <c r="D360">
-        <v>1278795.191897405</v>
+        <v>1279124.830925901</v>
       </c>
       <c r="E360">
-        <v>1259583.000631349</v>
+        <v>1259871.487147097</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6491,13 +6491,13 @@
         <v>13275499.07255545</v>
       </c>
       <c r="C361">
-        <v>18279766.419068</v>
+        <v>18279787.94746286</v>
       </c>
       <c r="D361">
-        <v>29542196.96482867</v>
+        <v>29565885.03867969</v>
       </c>
       <c r="E361">
-        <v>41171425.35732118</v>
+        <v>41214879.30271348</v>
       </c>
     </row>
     <row r="362" spans="1:5">
@@ -6508,13 +6508,13 @@
         <v>13475492.16468729</v>
       </c>
       <c r="C362">
-        <v>16775048.86786344</v>
+        <v>16776820.16615495</v>
       </c>
       <c r="D362">
-        <v>26694219.22636293</v>
+        <v>26816059.68788659</v>
       </c>
       <c r="E362">
-        <v>32316036.48372692</v>
+        <v>32511413.75685532</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6528,10 +6528,10 @@
         <v>1200866.035020359</v>
       </c>
       <c r="D363">
-        <v>2270402.836826769</v>
+        <v>2272990.316952801</v>
       </c>
       <c r="E363">
-        <v>3430276.505920694</v>
+        <v>3443451.478303698</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6545,10 +6545,10 @@
         <v>4069060.220268698</v>
       </c>
       <c r="D364">
-        <v>6593796.334924661</v>
+        <v>6595906.468376667</v>
       </c>
       <c r="E364">
-        <v>9055714.636440055</v>
+        <v>9063791.135474574</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6562,10 +6562,10 @@
         <v>3929947.050344982</v>
       </c>
       <c r="D365">
-        <v>6651133.694358788</v>
+        <v>6653262.176797334</v>
       </c>
       <c r="E365">
-        <v>9621696.801217558</v>
+        <v>9630278.081441734</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6576,13 +6576,13 @@
         <v>833677.6946785193</v>
       </c>
       <c r="C366">
-        <v>1085972.891079079</v>
+        <v>1085975.61227954</v>
       </c>
       <c r="D366">
-        <v>1777947.191793594</v>
+        <v>1778739.964951898</v>
       </c>
       <c r="E366">
-        <v>2220896.589727724</v>
+        <v>2223342.211058311</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6593,13 +6593,13 @@
         <v>926308.5496427992</v>
       </c>
       <c r="C367">
-        <v>1112460.034763934</v>
+        <v>1112462.822335139</v>
       </c>
       <c r="D367">
-        <v>1728559.769799327</v>
+        <v>1729330.521481012</v>
       </c>
       <c r="E367">
-        <v>1998806.930754951</v>
+        <v>2001007.98995248</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6610,13 +6610,13 @@
         <v>960276.4734913228</v>
       </c>
       <c r="C368">
-        <v>1184289.595425815</v>
+        <v>1184293.375846002</v>
       </c>
       <c r="D368">
-        <v>1946769.36485277</v>
+        <v>1947242.941698153</v>
       </c>
       <c r="E368">
-        <v>2487442.506214654</v>
+        <v>2489697.040593634</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -6627,13 +6627,13 @@
         <v>1018939.404607079</v>
       </c>
       <c r="C369">
-        <v>1138947.17844879</v>
+        <v>1138950.032390737</v>
       </c>
       <c r="D369">
-        <v>1679172.34780506</v>
+        <v>1679921.078010126</v>
       </c>
       <c r="E369">
-        <v>1702687.385457922</v>
+        <v>1704562.361811372</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6644,13 +6644,13 @@
         <v>403337.0289281703</v>
       </c>
       <c r="C370">
-        <v>604711.2532266891</v>
+        <v>604755.0565063905</v>
       </c>
       <c r="D370">
-        <v>1222389.145989648</v>
+        <v>1224863.112892005</v>
       </c>
       <c r="E370">
-        <v>1805509.922088744</v>
+        <v>1815529.01880283</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -6661,13 +6661,13 @@
         <v>504171.2861602128</v>
       </c>
       <c r="C371">
-        <v>643724.8824671207</v>
+        <v>643771.5117648672</v>
       </c>
       <c r="D371">
-        <v>1138086.446266224</v>
+        <v>1140389.794761522</v>
       </c>
       <c r="E371">
-        <v>1337414.757102774</v>
+        <v>1344836.310224318</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -6678,13 +6678,13 @@
         <v>466358.4396981969</v>
       </c>
       <c r="C372">
-        <v>624218.0678469049</v>
+        <v>624263.2841356288</v>
       </c>
       <c r="D372">
-        <v>1180237.796127936</v>
+        <v>1182626.453826763</v>
       </c>
       <c r="E372">
-        <v>1471156.232813051</v>
+        <v>1479319.94124675</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -6695,13 +6695,13 @@
         <v>5250901.859178973</v>
       </c>
       <c r="C373">
-        <v>7284012.449018565</v>
+        <v>7284015.983737358</v>
       </c>
       <c r="D373">
-        <v>11051068.65877783</v>
+        <v>11056185.26809003</v>
       </c>
       <c r="E373">
-        <v>15090973.8867446</v>
+        <v>15093775.98619007</v>
       </c>
     </row>
     <row r="374" spans="1:5">
@@ -6712,13 +6712,13 @@
         <v>3684597.135625223</v>
       </c>
       <c r="C374">
-        <v>5426649.491959856</v>
+        <v>5426652.465571597</v>
       </c>
       <c r="D374">
-        <v>8567327.010659989</v>
+        <v>8574752.374846159</v>
       </c>
       <c r="E374">
-        <v>12144794.9662962</v>
+        <v>12147320.93107022</v>
       </c>
     </row>
     <row r="375" spans="1:5">
@@ -6729,13 +6729,13 @@
         <v>7255278.375317183</v>
       </c>
       <c r="C375">
-        <v>8361748.98484274</v>
+        <v>8361753.04255564</v>
       </c>
       <c r="D375">
-        <v>10090106.16671019</v>
+        <v>10094777.8534735</v>
       </c>
       <c r="E375">
-        <v>10362005.11117486</v>
+        <v>10363929.13337475</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -6746,13 +6746,13 @@
         <v>4778820.045610787</v>
       </c>
       <c r="C376">
-        <v>5479207.066514349</v>
+        <v>5479213.697737399</v>
       </c>
       <c r="D376">
-        <v>7096897.893347477</v>
+        <v>7102434.927743275</v>
       </c>
       <c r="E376">
-        <v>7892359.234447868</v>
+        <v>7893903.137469982</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -6763,13 +6763,13 @@
         <v>4778820.045610787</v>
       </c>
       <c r="C377">
-        <v>5479207.066514349</v>
+        <v>5479213.697737399</v>
       </c>
       <c r="D377">
-        <v>7096897.893347477</v>
+        <v>7102434.927743275</v>
       </c>
       <c r="E377">
-        <v>7892359.234447868</v>
+        <v>7893903.137469982</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6780,13 +6780,13 @@
         <v>3328606.651620773</v>
       </c>
       <c r="C378">
-        <v>4237153.244104532</v>
+        <v>4237157.965340533</v>
       </c>
       <c r="D378">
-        <v>5812567.610694892</v>
+        <v>5813286.297515329</v>
       </c>
       <c r="E378">
-        <v>7485454.762836859</v>
+        <v>7489157.124341517</v>
       </c>
     </row>
     <row r="379" spans="1:5">
@@ -6797,13 +6797,13 @@
         <v>3224587.693757624</v>
       </c>
       <c r="C379">
-        <v>4366862.016883242</v>
+        <v>4366866.882646876</v>
       </c>
       <c r="D379">
-        <v>5870693.286801841</v>
+        <v>5871419.160490482</v>
       </c>
       <c r="E379">
-        <v>7411341.349343425</v>
+        <v>7415007.053803482</v>
       </c>
     </row>
     <row r="380" spans="1:5">
@@ -6814,13 +6814,13 @@
         <v>4472815.188115414</v>
       </c>
       <c r="C380">
-        <v>4583043.304847759</v>
+        <v>4583048.411490781</v>
       </c>
       <c r="D380">
-        <v>5289436.525732351</v>
+        <v>5290090.530738949</v>
       </c>
       <c r="E380">
-        <v>5558506.012007568</v>
+        <v>5561255.290352612</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -6831,13 +6831,13 @@
         <v>3328606.651620773</v>
       </c>
       <c r="C381">
-        <v>4237153.244104532</v>
+        <v>4237157.965340533</v>
       </c>
       <c r="D381">
-        <v>5812567.610694892</v>
+        <v>5813286.297515329</v>
       </c>
       <c r="E381">
-        <v>7485454.762836859</v>
+        <v>7489157.124341517</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -6848,13 +6848,13 @@
         <v>2224549.727039301</v>
       </c>
       <c r="C382">
-        <v>2470135.415723787</v>
+        <v>2470207.823427392</v>
       </c>
       <c r="D382">
-        <v>2908813.204061891</v>
+        <v>2909579.485573197</v>
       </c>
       <c r="E382">
-        <v>3071643.390548381</v>
+        <v>3073046.243779544</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -6865,13 +6865,13 @@
         <v>5555892.970667209</v>
       </c>
       <c r="C383">
-        <v>7640487.980989479</v>
+        <v>7640488.094421939</v>
       </c>
       <c r="D383">
-        <v>11325667.41781012</v>
+        <v>11329135.91935968</v>
       </c>
       <c r="E383">
-        <v>15261823.77155999</v>
+        <v>15277188.22040863</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -6882,13 +6882,13 @@
         <v>8903269.249489062</v>
       </c>
       <c r="C384">
-        <v>9621619.280150944</v>
+        <v>9621627.139646441</v>
       </c>
       <c r="D384">
-        <v>12119047.077855</v>
+        <v>12120782.68619616</v>
       </c>
       <c r="E384">
-        <v>13360135.12907218</v>
+        <v>13364356.85278242</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -6899,13 +6899,13 @@
         <v>1436759.946208561</v>
       </c>
       <c r="C385">
-        <v>1867649.781243417</v>
+        <v>1867650.039718897</v>
       </c>
       <c r="D385">
-        <v>2554820.799281181</v>
+        <v>2556206.72989527</v>
       </c>
       <c r="E385">
-        <v>3303721.744866451</v>
+        <v>3306528.915741528</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -6916,13 +6916,13 @@
         <v>1666589.28349111</v>
       </c>
       <c r="C386">
-        <v>2244908.62251453</v>
+        <v>2244910.745969918</v>
       </c>
       <c r="D386">
-        <v>3485906.683357427</v>
+        <v>3488544.1240234</v>
       </c>
       <c r="E386">
-        <v>4546820.190055965</v>
+        <v>4558541.824334994</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -6933,13 +6933,13 @@
         <v>1910480.398148346</v>
       </c>
       <c r="C387">
-        <v>2329092.695858825</v>
+        <v>2329094.898943789</v>
       </c>
       <c r="D387">
-        <v>3392949.171801229</v>
+        <v>3395516.280716109</v>
       </c>
       <c r="E387">
-        <v>3953756.687005187</v>
+        <v>3963949.412465212</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -6953,10 +6953,10 @@
         <v>3278087.961729859</v>
       </c>
       <c r="D388">
-        <v>7320400.624522304</v>
+        <v>7320486.302808174</v>
       </c>
       <c r="E388">
-        <v>11460725.57906932</v>
+        <v>11461335.78035495</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -6967,13 +6967,13 @@
         <v>212358.5215624084</v>
       </c>
       <c r="C389">
-        <v>291556.436464904</v>
+        <v>291558.291938576</v>
       </c>
       <c r="D389">
-        <v>707896.4243986116</v>
+        <v>707927.7672518732</v>
       </c>
       <c r="E389">
-        <v>997899.2727962242</v>
+        <v>998424.774627163</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -6984,13 +6984,13 @@
         <v>212358.5215624084</v>
       </c>
       <c r="C390">
-        <v>300667.5751044322</v>
+        <v>300669.4885616565</v>
       </c>
       <c r="D390">
-        <v>707896.4243986116</v>
+        <v>707927.7672518732</v>
       </c>
       <c r="E390">
-        <v>952540.2149418504</v>
+        <v>953041.8303259283</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -7004,10 +7004,10 @@
         <v>3278087.961729859</v>
       </c>
       <c r="D391">
-        <v>7320400.624522304</v>
+        <v>7320486.302808174</v>
       </c>
       <c r="E391">
-        <v>11460725.57906932</v>
+        <v>11461335.78035495</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -7018,13 +7018,13 @@
         <v>240300.4322943042</v>
       </c>
       <c r="C392">
-        <v>309778.7137439605</v>
+        <v>309780.685184737</v>
       </c>
       <c r="D392">
-        <v>682614.4092415184</v>
+        <v>682644.6327071635</v>
       </c>
       <c r="E392">
-        <v>816463.0413787289</v>
+        <v>816892.9974222243</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7038,10 +7038,10 @@
         <v>650355.6997427943</v>
       </c>
       <c r="D393">
-        <v>1418999.632684212</v>
+        <v>1419136.910392389</v>
       </c>
       <c r="E393">
-        <v>2008138.784661976</v>
+        <v>2008625.014044916</v>
       </c>
     </row>
     <row r="394" spans="1:5">
@@ -7055,10 +7055,10 @@
         <v>635404.9940015805</v>
       </c>
       <c r="D394">
-        <v>1438175.30339616</v>
+        <v>1438314.436208503</v>
       </c>
       <c r="E394">
-        <v>2106899.708497811</v>
+        <v>2107409.850801223</v>
       </c>
     </row>
     <row r="395" spans="1:5">
@@ -7069,13 +7069,13 @@
         <v>354134.7699629247</v>
       </c>
       <c r="C395">
-        <v>545702.3731537205</v>
+        <v>545713.0560720611</v>
       </c>
       <c r="D395">
-        <v>1328148.073923048</v>
+        <v>1328297.466284787</v>
       </c>
       <c r="E395">
-        <v>2226168.308120601</v>
+        <v>2227077.163272884</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7086,13 +7086,13 @@
         <v>445351.3016200417</v>
       </c>
       <c r="C396">
-        <v>595311.6798040587</v>
+        <v>595323.3338967939</v>
       </c>
       <c r="D396">
-        <v>1246415.884758553</v>
+        <v>1246556.083744185</v>
       </c>
       <c r="E396">
-        <v>1704410.110904835</v>
+        <v>1705105.953130802</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7106,10 +7106,10 @@
         <v>218859.2024091575</v>
       </c>
       <c r="D397">
-        <v>476096.1849069651</v>
+        <v>476151.6225934501</v>
       </c>
       <c r="E397">
-        <v>739416.5296905406</v>
+        <v>739912.3411775817</v>
       </c>
     </row>
     <row r="398" spans="1:5">
@@ -7123,10 +7123,10 @@
         <v>218859.2024091575</v>
       </c>
       <c r="D398">
-        <v>476096.1849069651</v>
+        <v>476151.6225934501</v>
       </c>
       <c r="E398">
-        <v>739416.5296905406</v>
+        <v>739912.3411775817</v>
       </c>
     </row>
     <row r="399" spans="1:5">
@@ -7140,10 +7140,10 @@
         <v>2245705.750408615</v>
       </c>
       <c r="D399">
-        <v>6533025.18417887</v>
+        <v>6533176.888610903</v>
       </c>
       <c r="E399">
-        <v>11357798.2068569</v>
+        <v>11363847.1441103</v>
       </c>
     </row>
     <row r="400" spans="1:5">
@@ -7157,10 +7157,10 @@
         <v>1984152.219165066</v>
       </c>
       <c r="D400">
-        <v>5261735.788301196</v>
+        <v>5262039.907685655</v>
       </c>
       <c r="E400">
-        <v>7716999.890582673</v>
+        <v>7723633.243939381</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7174,10 +7174,10 @@
         <v>2333772.642581501</v>
       </c>
       <c r="D401">
-        <v>6320569.080628338</v>
+        <v>6320715.851582906</v>
       </c>
       <c r="E401">
-        <v>10047283.02914264</v>
+        <v>10052634.01209757</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7191,10 +7191,10 @@
         <v>178018.5113000587</v>
       </c>
       <c r="D402">
-        <v>503029.1051008693</v>
+        <v>503052.0923590238</v>
       </c>
       <c r="E402">
-        <v>841471.037972871</v>
+        <v>842519.5421084408</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7208,10 +7208,10 @@
         <v>1959350.316425502</v>
       </c>
       <c r="D403">
-        <v>5365928.576188348</v>
+        <v>5366238.717738836</v>
       </c>
       <c r="E403">
-        <v>8247543.633060232</v>
+        <v>8254633.029460213</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -7225,10 +7225,10 @@
         <v>426759.5480956581</v>
       </c>
       <c r="D404">
-        <v>1303463.276814635</v>
+        <v>1303489.037231933</v>
       </c>
       <c r="E404">
-        <v>2133671.393373201</v>
+        <v>2134940.375309438</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -7242,10 +7242,10 @@
         <v>440751.6644266633</v>
       </c>
       <c r="D405">
-        <v>1256911.016928398</v>
+        <v>1256935.857330792</v>
       </c>
       <c r="E405">
-        <v>1915949.822620834</v>
+        <v>1917089.316604393</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -7259,10 +7259,10 @@
         <v>426759.5480956581</v>
       </c>
       <c r="D406">
-        <v>1303463.276814635</v>
+        <v>1303489.037231933</v>
       </c>
       <c r="E406">
-        <v>2133671.393373201</v>
+        <v>2134940.375309438</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7276,10 +7276,10 @@
         <v>379878.352515318</v>
       </c>
       <c r="D407">
-        <v>1334230.829514612</v>
+        <v>1334258.551356816</v>
       </c>
       <c r="E407">
-        <v>2561050.643809587</v>
+        <v>2562113.620442502</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -7293,10 +7293,10 @@
         <v>416640.7737264778</v>
       </c>
       <c r="D408">
-        <v>1248151.42115883</v>
+        <v>1248177.354495086</v>
       </c>
       <c r="E408">
-        <v>1951276.680997781</v>
+        <v>1952086.567956192</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -7310,10 +7310,10 @@
         <v>386005.4227171779</v>
       </c>
       <c r="D409">
-        <v>1312710.977425666</v>
+        <v>1312738.252141383</v>
       </c>
       <c r="E409">
-        <v>2439095.851247226</v>
+        <v>2440108.20994524</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -7324,13 +7324,13 @@
         <v>2034450.176678515</v>
       </c>
       <c r="C410">
-        <v>3404716.264877077</v>
+        <v>3404740.713587023</v>
       </c>
       <c r="D410">
-        <v>7533057.483481361</v>
+        <v>7537738.501421828</v>
       </c>
       <c r="E410">
-        <v>11899883.41762319</v>
+        <v>11926383.97051189</v>
       </c>
     </row>
     <row r="411" spans="1:5">
@@ -7341,13 +7341,13 @@
         <v>377203.602126974</v>
       </c>
       <c r="C411">
-        <v>800070.0005366022</v>
+        <v>800070.5468573384</v>
       </c>
       <c r="D411">
-        <v>2467718.008544689</v>
+        <v>2468297.395264625</v>
       </c>
       <c r="E411">
-        <v>5164376.448637566</v>
+        <v>5174771.101919216</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -7358,13 +7358,13 @@
         <v>646634.746503384</v>
       </c>
       <c r="C412">
-        <v>981217.9251863989</v>
+        <v>981218.5952023962</v>
       </c>
       <c r="D412">
-        <v>2209896.72406987</v>
+        <v>2210415.577848918</v>
       </c>
       <c r="E412">
-        <v>3359955.761764199</v>
+        <v>3366718.548236599</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -7375,13 +7375,13 @@
         <v>1464030.372546368</v>
       </c>
       <c r="C413">
-        <v>2255411.646414727</v>
+        <v>2255905.660893411</v>
       </c>
       <c r="D413">
-        <v>4893689.580754822</v>
+        <v>4905294.792780179</v>
       </c>
       <c r="E413">
-        <v>6715360.580370617</v>
+        <v>6752848.55298306</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -7392,13 +7392,13 @@
         <v>2034450.176678515</v>
       </c>
       <c r="C414">
-        <v>3404716.264877077</v>
+        <v>3404740.713587023</v>
       </c>
       <c r="D414">
-        <v>7533057.483481361</v>
+        <v>7537738.501421828</v>
       </c>
       <c r="E414">
-        <v>11899883.41762319</v>
+        <v>11926383.97051189</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -7412,10 +7412,10 @@
         <v>1225044.855546764</v>
       </c>
       <c r="D415">
-        <v>2575133.959469709</v>
+        <v>2575922.902504109</v>
       </c>
       <c r="E415">
-        <v>3787039.898147089</v>
+        <v>3789965.13357009</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -7429,10 +7429,10 @@
         <v>1311315.620021889</v>
       </c>
       <c r="D416">
-        <v>2494661.023236281</v>
+        <v>2495425.311800856</v>
       </c>
       <c r="E416">
-        <v>3122646.93355988</v>
+        <v>3125058.969785864</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -7443,13 +7443,13 @@
         <v>167130.456254998</v>
       </c>
       <c r="C417">
-        <v>242819.7843659542</v>
+        <v>242823.0139433942</v>
       </c>
       <c r="D417">
-        <v>616835.5157995241</v>
+        <v>617398.7514678879</v>
       </c>
       <c r="E417">
-        <v>1047332.260200186</v>
+        <v>1051026.289026803</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7460,13 +7460,13 @@
         <v>200556.5475059976</v>
       </c>
       <c r="C418">
-        <v>264894.3102174046</v>
+        <v>264897.8333927937</v>
       </c>
       <c r="D418">
-        <v>585993.7400095479</v>
+        <v>586528.8138944935</v>
       </c>
       <c r="E418">
-        <v>771718.5075159264</v>
+        <v>774440.4234934335</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -7480,10 +7480,10 @@
         <v>750304.5946782082</v>
       </c>
       <c r="D419">
-        <v>1447494.335762299</v>
+        <v>1447633.796523387</v>
       </c>
       <c r="E419">
-        <v>2329245.595018013</v>
+        <v>2331206.754500018</v>
       </c>
     </row>
     <row r="420" spans="1:5">
@@ -7497,10 +7497,10 @@
         <v>750304.5946782082</v>
       </c>
       <c r="D420">
-        <v>1447494.335762299</v>
+        <v>1447633.796523387</v>
       </c>
       <c r="E420">
-        <v>2329245.595018013</v>
+        <v>2331206.754500018</v>
       </c>
     </row>
     <row r="421" spans="1:5">
@@ -7514,10 +7514,10 @@
         <v>732112.9053276691</v>
       </c>
       <c r="D421">
-        <v>1406226.578938466</v>
+        <v>1406421.628261099</v>
       </c>
       <c r="E421">
-        <v>2262507.018323545</v>
+        <v>2264547.897528261</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -7531,10 +7531,10 @@
         <v>732112.9053276691</v>
       </c>
       <c r="D422">
-        <v>1406226.578938466</v>
+        <v>1406421.628261099</v>
       </c>
       <c r="E422">
-        <v>2262507.018323545</v>
+        <v>2264547.897528261</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -7548,10 +7548,10 @@
         <v>750304.5946782082</v>
       </c>
       <c r="D423">
-        <v>1447494.335762299</v>
+        <v>1447633.796523387</v>
       </c>
       <c r="E423">
-        <v>2329245.595018013</v>
+        <v>2331206.754500018</v>
       </c>
     </row>
     <row r="424" spans="1:5">
@@ -7565,10 +7565,10 @@
         <v>750304.5946782082</v>
       </c>
       <c r="D424">
-        <v>1447494.335762299</v>
+        <v>1447633.796523387</v>
       </c>
       <c r="E424">
-        <v>2329245.595018013</v>
+        <v>2331206.754500018</v>
       </c>
     </row>
     <row r="425" spans="1:5">
@@ -7582,10 +7582,10 @@
         <v>732112.9053276691</v>
       </c>
       <c r="D425">
-        <v>1406226.578938466</v>
+        <v>1406421.628261099</v>
       </c>
       <c r="E425">
-        <v>2262507.018323545</v>
+        <v>2264547.897528261</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -7599,10 +7599,10 @@
         <v>750304.5946782082</v>
       </c>
       <c r="D426">
-        <v>1447494.335762299</v>
+        <v>1447633.796523387</v>
       </c>
       <c r="E426">
-        <v>2329245.595018013</v>
+        <v>2331206.754500018</v>
       </c>
     </row>
     <row r="427" spans="1:5">
@@ -7616,10 +7616,10 @@
         <v>750304.5946782082</v>
       </c>
       <c r="D427">
-        <v>1447494.335762299</v>
+        <v>1447633.796523387</v>
       </c>
       <c r="E427">
-        <v>2329245.595018013</v>
+        <v>2331206.754500018</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -7633,10 +7633,10 @@
         <v>750304.5946782082</v>
       </c>
       <c r="D428">
-        <v>1447494.335762299</v>
+        <v>1447633.796523387</v>
       </c>
       <c r="E428">
-        <v>2329245.595018013</v>
+        <v>2331206.754500018</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -7650,10 +7650,10 @@
         <v>750304.5946782082</v>
       </c>
       <c r="D429">
-        <v>1447494.335762299</v>
+        <v>1447633.796523387</v>
       </c>
       <c r="E429">
-        <v>2329245.595018013</v>
+        <v>2331206.754500018</v>
       </c>
     </row>
     <row r="430" spans="1:5">
@@ -7667,10 +7667,10 @@
         <v>750304.5946782082</v>
       </c>
       <c r="D430">
-        <v>1447494.335762299</v>
+        <v>1447633.796523387</v>
       </c>
       <c r="E430">
-        <v>2329245.595018013</v>
+        <v>2331206.754500018</v>
       </c>
     </row>
     <row r="431" spans="1:5">
@@ -7684,10 +7684,10 @@
         <v>732112.9053276691</v>
       </c>
       <c r="D431">
-        <v>1406226.578938466</v>
+        <v>1406421.628261099</v>
       </c>
       <c r="E431">
-        <v>2262507.018323545</v>
+        <v>2264547.897528261</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -7701,10 +7701,10 @@
         <v>750304.5946782082</v>
       </c>
       <c r="D432">
-        <v>1447494.335762299</v>
+        <v>1447633.796523387</v>
       </c>
       <c r="E432">
-        <v>2329245.595018013</v>
+        <v>2331206.754500018</v>
       </c>
     </row>
     <row r="433" spans="1:5">
@@ -7718,10 +7718,10 @@
         <v>750304.5946782082</v>
       </c>
       <c r="D433">
-        <v>1447494.335762299</v>
+        <v>1447633.796523387</v>
       </c>
       <c r="E433">
-        <v>2329245.595018013</v>
+        <v>2331206.754500018</v>
       </c>
     </row>
     <row r="434" spans="1:5">
@@ -7735,10 +7735,10 @@
         <v>869489.946226708</v>
       </c>
       <c r="D434">
-        <v>1861898.076740356</v>
+        <v>1861922.846408385</v>
       </c>
       <c r="E434">
-        <v>2983812.807771442</v>
+        <v>2985011.334921125</v>
       </c>
     </row>
     <row r="435" spans="1:5">
@@ -7752,10 +7752,10 @@
         <v>786033.38490098</v>
       </c>
       <c r="D435">
-        <v>1375119.618974184</v>
+        <v>1375252.106697218</v>
       </c>
       <c r="E435">
-        <v>1688703.056388059</v>
+        <v>1690124.897012512</v>
       </c>
     </row>
     <row r="436" spans="1:5">
@@ -7769,10 +7769,10 @@
         <v>315019.721778699</v>
       </c>
       <c r="D436">
-        <v>679334.5814951025</v>
+        <v>679672.414568693</v>
       </c>
       <c r="E436">
-        <v>1006587.549484466</v>
+        <v>1008503.156913621</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -7786,10 +7786,10 @@
         <v>225200.3660087122</v>
       </c>
       <c r="D437">
-        <v>497371.9497010251</v>
+        <v>497386.8801670282</v>
       </c>
       <c r="E437">
-        <v>757333.470112125</v>
+        <v>757485.9117685283</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -7803,10 +7803,10 @@
         <v>225200.3660087122</v>
       </c>
       <c r="D438">
-        <v>497371.9497010251</v>
+        <v>497386.8801670282</v>
       </c>
       <c r="E438">
-        <v>757333.470112125</v>
+        <v>757485.9117685283</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -7820,10 +7820,10 @@
         <v>225200.3660087122</v>
       </c>
       <c r="D439">
-        <v>497371.9497010251</v>
+        <v>497386.8801670282</v>
       </c>
       <c r="E439">
-        <v>757333.470112125</v>
+        <v>757485.9117685283</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -7837,10 +7837,10 @@
         <v>225200.3660087122</v>
       </c>
       <c r="D440">
-        <v>497371.9497010251</v>
+        <v>497386.8801670282</v>
       </c>
       <c r="E440">
-        <v>757333.470112125</v>
+        <v>757485.9117685283</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -7854,10 +7854,10 @@
         <v>225200.3660087122</v>
       </c>
       <c r="D441">
-        <v>497371.9497010251</v>
+        <v>497386.8801670282</v>
       </c>
       <c r="E441">
-        <v>757333.470112125</v>
+        <v>757485.9117685283</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -7871,10 +7871,10 @@
         <v>225200.3660087122</v>
       </c>
       <c r="D442">
-        <v>497371.9497010251</v>
+        <v>497386.8801670282</v>
       </c>
       <c r="E442">
-        <v>757333.470112125</v>
+        <v>757485.9117685283</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -7888,10 +7888,10 @@
         <v>225200.3660087122</v>
       </c>
       <c r="D443">
-        <v>497371.9497010251</v>
+        <v>497386.8801670282</v>
       </c>
       <c r="E443">
-        <v>757333.470112125</v>
+        <v>757485.9117685283</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -7905,10 +7905,10 @@
         <v>225200.3660087122</v>
       </c>
       <c r="D444">
-        <v>497371.9497010251</v>
+        <v>497386.8801670282</v>
       </c>
       <c r="E444">
-        <v>757333.470112125</v>
+        <v>757485.9117685283</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -7922,10 +7922,10 @@
         <v>225200.3660087122</v>
       </c>
       <c r="D445">
-        <v>497371.9497010251</v>
+        <v>497386.8801670282</v>
       </c>
       <c r="E445">
-        <v>757333.470112125</v>
+        <v>757485.9117685283</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -7939,10 +7939,10 @@
         <v>225200.3660087122</v>
       </c>
       <c r="D446">
-        <v>497371.9497010251</v>
+        <v>497386.8801670282</v>
       </c>
       <c r="E446">
-        <v>757333.470112125</v>
+        <v>757485.9117685283</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -7956,10 +7956,10 @@
         <v>225200.3660087122</v>
       </c>
       <c r="D447">
-        <v>497371.9497010251</v>
+        <v>497386.8801670282</v>
       </c>
       <c r="E447">
-        <v>757333.470112125</v>
+        <v>757485.9117685283</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -7973,10 +7973,10 @@
         <v>464216.6846876254</v>
       </c>
       <c r="D448">
-        <v>740587.8704508013</v>
+        <v>740712.9247464103</v>
       </c>
       <c r="E448">
-        <v>1112887.015382066</v>
+        <v>1113578.959293007</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -7990,10 +7990,10 @@
         <v>464216.6846876254</v>
       </c>
       <c r="D449">
-        <v>740587.8704508013</v>
+        <v>740712.9247464103</v>
       </c>
       <c r="E449">
-        <v>1112887.015382066</v>
+        <v>1113578.959293007</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -8007,10 +8007,10 @@
         <v>464216.6846876254</v>
       </c>
       <c r="D450">
-        <v>740587.8704508013</v>
+        <v>740712.9247464103</v>
       </c>
       <c r="E450">
-        <v>1112887.015382066</v>
+        <v>1113578.959293007</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -8024,10 +8024,10 @@
         <v>464216.6846876254</v>
       </c>
       <c r="D451">
-        <v>740587.8704508013</v>
+        <v>740712.9247464103</v>
       </c>
       <c r="E451">
-        <v>1112887.015382066</v>
+        <v>1113578.959293007</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -8041,10 +8041,10 @@
         <v>464216.6846876254</v>
       </c>
       <c r="D452">
-        <v>740587.8704508013</v>
+        <v>740712.9247464103</v>
       </c>
       <c r="E452">
-        <v>1112887.015382066</v>
+        <v>1113578.959293007</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -8058,10 +8058,10 @@
         <v>412637.053055667</v>
       </c>
       <c r="D453">
-        <v>827715.8552097192</v>
+        <v>827855.6217753998</v>
       </c>
       <c r="E453">
-        <v>1571134.609951152</v>
+        <v>1572111.471943069</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -8072,13 +8072,13 @@
         <v>649846.2182508891</v>
       </c>
       <c r="C454">
-        <v>820590.3512673328</v>
+        <v>820712.4939006914</v>
       </c>
       <c r="D454">
-        <v>1488133.279549983</v>
+        <v>1488251.665615701</v>
       </c>
       <c r="E454">
-        <v>2124194.045368572</v>
+        <v>2124866.018806732</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -8089,13 +8089,13 @@
         <v>649846.2182508891</v>
       </c>
       <c r="C455">
-        <v>820590.3512673328</v>
+        <v>820712.4939006914</v>
       </c>
       <c r="D455">
-        <v>1488133.279549983</v>
+        <v>1488251.665615701</v>
       </c>
       <c r="E455">
-        <v>2124194.045368572</v>
+        <v>2124866.018806732</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -8106,13 +8106,13 @@
         <v>649846.2182508891</v>
       </c>
       <c r="C456">
-        <v>820590.3512673328</v>
+        <v>820712.4939006914</v>
       </c>
       <c r="D456">
-        <v>1488133.279549983</v>
+        <v>1488251.665615701</v>
       </c>
       <c r="E456">
-        <v>2124194.045368572</v>
+        <v>2124866.018806732</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -8123,13 +8123,13 @@
         <v>649846.2182508891</v>
       </c>
       <c r="C457">
-        <v>820590.3512673328</v>
+        <v>820712.4939006914</v>
       </c>
       <c r="D457">
-        <v>1488133.279549983</v>
+        <v>1488251.665615701</v>
       </c>
       <c r="E457">
-        <v>2124194.045368572</v>
+        <v>2124866.018806732</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -8140,13 +8140,13 @@
         <v>649846.2182508891</v>
       </c>
       <c r="C458">
-        <v>820590.3512673328</v>
+        <v>820712.4939006914</v>
       </c>
       <c r="D458">
-        <v>1488133.279549983</v>
+        <v>1488251.665615701</v>
       </c>
       <c r="E458">
-        <v>2124194.045368572</v>
+        <v>2124866.018806732</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -8157,13 +8157,13 @@
         <v>747323.1509885226</v>
       </c>
       <c r="C459">
-        <v>885373.8000515959</v>
+        <v>885505.5855244301</v>
       </c>
       <c r="D459">
-        <v>1407693.642817551</v>
+        <v>1407805.629636474</v>
       </c>
       <c r="E459">
-        <v>1749336.272656471</v>
+        <v>1749889.66254672</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -8174,13 +8174,13 @@
         <v>649846.2182508891</v>
       </c>
       <c r="C460">
-        <v>820590.3512673328</v>
+        <v>820712.4939006914</v>
       </c>
       <c r="D460">
-        <v>1488133.279549983</v>
+        <v>1488251.665615701</v>
       </c>
       <c r="E460">
-        <v>2124194.045368572</v>
+        <v>2124866.018806732</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -8191,13 +8191,13 @@
         <v>649846.2182508891</v>
       </c>
       <c r="C461">
-        <v>820590.3512673328</v>
+        <v>820712.4939006914</v>
       </c>
       <c r="D461">
-        <v>1488133.279549983</v>
+        <v>1488251.665615701</v>
       </c>
       <c r="E461">
-        <v>2124194.045368572</v>
+        <v>2124866.018806732</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -8208,13 +8208,13 @@
         <v>747323.1509885226</v>
       </c>
       <c r="C462">
-        <v>885373.8000515959</v>
+        <v>885505.5855244301</v>
       </c>
       <c r="D462">
-        <v>1407693.642817551</v>
+        <v>1407805.629636474</v>
       </c>
       <c r="E462">
-        <v>1749336.272656471</v>
+        <v>1749889.66254672</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -8228,10 +8228,10 @@
         <v>732440.1995668224</v>
       </c>
       <c r="D463">
-        <v>1447494.335762299</v>
+        <v>1447633.796523387</v>
       </c>
       <c r="E463">
-        <v>2387476.734893463</v>
+        <v>2389486.923362518</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -8245,10 +8245,10 @@
         <v>732440.1995668224</v>
       </c>
       <c r="D464">
-        <v>1447494.335762299</v>
+        <v>1447633.796523387</v>
       </c>
       <c r="E464">
-        <v>2387476.734893463</v>
+        <v>2389486.923362518</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -8262,10 +8262,10 @@
         <v>936373.7882441471</v>
       </c>
       <c r="D465">
-        <v>1716437.289495016</v>
+        <v>1716460.12403273</v>
       </c>
       <c r="E465">
-        <v>2261922.612342867</v>
+        <v>2262831.17324666</v>
       </c>
     </row>
     <row r="466" spans="1:5">
@@ -8279,10 +8279,10 @@
         <v>842736.4094197323</v>
       </c>
       <c r="D466">
-        <v>1832805.919291288</v>
+        <v>1832830.301933254</v>
       </c>
       <c r="E466">
-        <v>3080064.833828585</v>
+        <v>3081302.023144388</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -8296,10 +8296,10 @@
         <v>732440.1995668224</v>
       </c>
       <c r="D467">
-        <v>1447494.335762299</v>
+        <v>1447633.796523387</v>
       </c>
       <c r="E467">
-        <v>2387476.734893463</v>
+        <v>2389486.923362518</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -8313,10 +8313,10 @@
         <v>412637.053055667</v>
       </c>
       <c r="D468">
-        <v>827715.8552097192</v>
+        <v>827855.6217753998</v>
       </c>
       <c r="E468">
-        <v>1571134.609951152</v>
+        <v>1572111.471943069</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -8330,10 +8330,10 @@
         <v>490006.5005036046</v>
       </c>
       <c r="D469">
-        <v>740587.8704508013</v>
+        <v>740712.9247464103</v>
       </c>
       <c r="E469">
-        <v>981959.1312194703</v>
+        <v>982569.669964418</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -8347,10 +8347,10 @@
         <v>490006.5005036046</v>
       </c>
       <c r="D470">
-        <v>740587.8704508013</v>
+        <v>740712.9247464103</v>
       </c>
       <c r="E470">
-        <v>981959.1312194703</v>
+        <v>982569.669964418</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -8364,10 +8364,10 @@
         <v>803897.780012366</v>
       </c>
       <c r="D471">
-        <v>1375119.618974184</v>
+        <v>1375252.106697218</v>
       </c>
       <c r="E471">
-        <v>1688703.056388059</v>
+        <v>1690124.897012512</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -8378,13 +8378,13 @@
         <v>779815.4619010669</v>
       </c>
       <c r="C472">
-        <v>928562.7659077713</v>
+        <v>928700.979940256</v>
       </c>
       <c r="D472">
-        <v>1407693.642817551</v>
+        <v>1407805.629636474</v>
       </c>
       <c r="E472">
-        <v>1499431.090848404</v>
+        <v>1499905.425040046</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -8398,10 +8398,10 @@
         <v>949750.5566476348</v>
       </c>
       <c r="D473">
-        <v>1716437.289495016</v>
+        <v>1716460.12403273</v>
       </c>
       <c r="E473">
-        <v>2213796.599314296</v>
+        <v>2214685.829135029</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -8415,10 +8415,10 @@
         <v>949750.5566476348</v>
       </c>
       <c r="D474">
-        <v>1716437.289495016</v>
+        <v>1716460.12403273</v>
       </c>
       <c r="E474">
-        <v>2213796.599314296</v>
+        <v>2214685.829135029</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -8432,10 +8432,10 @@
         <v>326687.1188816137</v>
       </c>
       <c r="D475">
-        <v>679334.5814951025</v>
+        <v>679672.414568693</v>
       </c>
       <c r="E475">
-        <v>910722.0685811839</v>
+        <v>912455.2372075614</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -8449,10 +8449,10 @@
         <v>497427.0682672565</v>
       </c>
       <c r="D476">
-        <v>932413.0506363312</v>
+        <v>932514.7134191419</v>
       </c>
       <c r="E476">
-        <v>1182324.60992079</v>
+        <v>1182870.806832205</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -8466,10 +8466,10 @@
         <v>485294.7007485429</v>
       </c>
       <c r="D477">
-        <v>960667.9915647048</v>
+        <v>960772.7350379039</v>
       </c>
       <c r="E477">
-        <v>1229617.594317622</v>
+        <v>1230185.639105493</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -8480,13 +8480,13 @@
         <v>1456306.970522957</v>
       </c>
       <c r="C478">
-        <v>2252318.843670072</v>
+        <v>2252323.326611823</v>
       </c>
       <c r="D478">
-        <v>5194674.421615718</v>
+        <v>5195360.792110935</v>
       </c>
       <c r="E478">
-        <v>8925943.386271561</v>
+        <v>8932749.371661633</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -8500,10 +8500,10 @@
         <v>7249240.179175523</v>
       </c>
       <c r="D479">
-        <v>14776590.86530416</v>
+        <v>14777215.38841655</v>
       </c>
       <c r="E479">
-        <v>21358591.07164622</v>
+        <v>21365438.44764391</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -8514,13 +8514,13 @@
         <v>1477130.995542239</v>
       </c>
       <c r="C480">
-        <v>2311127.173544125</v>
+        <v>2311130.16227743</v>
       </c>
       <c r="D480">
-        <v>5358609.902083908</v>
+        <v>5359157.856988363</v>
       </c>
       <c r="E480">
-        <v>9209632.696296651</v>
+        <v>9216088.695831226</v>
       </c>
     </row>
     <row r="481" spans="1:5">
@@ -8531,13 +8531,13 @@
         <v>1456306.970522957</v>
       </c>
       <c r="C481">
-        <v>2252318.843670072</v>
+        <v>2252323.326611823</v>
       </c>
       <c r="D481">
-        <v>5194674.421615718</v>
+        <v>5195360.792110935</v>
       </c>
       <c r="E481">
-        <v>8925943.386271561</v>
+        <v>8932749.371661633</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -8548,13 +8548,13 @@
         <v>1456306.970522957</v>
       </c>
       <c r="C482">
-        <v>2252318.843670072</v>
+        <v>2252323.326611823</v>
       </c>
       <c r="D482">
-        <v>5194674.421615718</v>
+        <v>5195360.792110935</v>
       </c>
       <c r="E482">
-        <v>8925943.386271561</v>
+        <v>8932749.371661633</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -8565,13 +8565,13 @@
         <v>1456306.970522957</v>
       </c>
       <c r="C483">
-        <v>2252318.843670072</v>
+        <v>2252323.326611823</v>
       </c>
       <c r="D483">
-        <v>5194674.421615718</v>
+        <v>5195360.792110935</v>
       </c>
       <c r="E483">
-        <v>8925943.386271561</v>
+        <v>8932749.371661633</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -8582,13 +8582,13 @@
         <v>1456306.970522957</v>
       </c>
       <c r="C484">
-        <v>2252318.843670072</v>
+        <v>2252323.326611823</v>
       </c>
       <c r="D484">
-        <v>5194674.421615718</v>
+        <v>5195360.792110935</v>
       </c>
       <c r="E484">
-        <v>8925943.386271561</v>
+        <v>8932749.371661633</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -8599,13 +8599,13 @@
         <v>1477130.995542239</v>
       </c>
       <c r="C485">
-        <v>2311127.173544125</v>
+        <v>2311130.16227743</v>
       </c>
       <c r="D485">
-        <v>5358609.902083908</v>
+        <v>5359157.856988363</v>
       </c>
       <c r="E485">
-        <v>9209632.696296651</v>
+        <v>9216088.695831226</v>
       </c>
     </row>
     <row r="486" spans="1:5">
@@ -8619,10 +8619,10 @@
         <v>4134697.034808846</v>
       </c>
       <c r="D486">
-        <v>9664453.640321938</v>
+        <v>9665034.489445295</v>
       </c>
       <c r="E486">
-        <v>16642804.33786662</v>
+        <v>16649331.65169485</v>
       </c>
     </row>
     <row r="487" spans="1:5">
@@ -8633,13 +8633,13 @@
         <v>804541.2987478651</v>
       </c>
       <c r="C487">
-        <v>1020151.835832849</v>
+        <v>1020153.12431807</v>
       </c>
       <c r="D487">
-        <v>1843613.904992551</v>
+        <v>1843694.655693129</v>
       </c>
       <c r="E487">
-        <v>2266872.919823304</v>
+        <v>2267860.27007749</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -8650,13 +8650,13 @@
         <v>218353.8125108333</v>
       </c>
       <c r="C488">
-        <v>298747.7291085532</v>
+        <v>298767.109466924</v>
       </c>
       <c r="D488">
-        <v>710301.0649549273</v>
+        <v>710582.0903239166</v>
       </c>
       <c r="E488">
-        <v>1145206.348363032</v>
+        <v>1146836.994078199</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -8667,13 +8667,13 @@
         <v>262024.575013</v>
       </c>
       <c r="C489">
-        <v>337714.8242096688</v>
+        <v>337736.7324408707</v>
       </c>
       <c r="D489">
-        <v>651109.3095420167</v>
+        <v>651366.916130257</v>
       </c>
       <c r="E489">
-        <v>946040.0269085914</v>
+        <v>947387.0820645991</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -8684,13 +8684,13 @@
         <v>2690162.738076118</v>
       </c>
       <c r="C490">
-        <v>3843563.943784507</v>
+        <v>3843594.717746332</v>
       </c>
       <c r="D490">
-        <v>7485358.680450602</v>
+        <v>7487375.014692368</v>
       </c>
       <c r="E490">
-        <v>11004962.12992691</v>
+        <v>11016963.26848035</v>
       </c>
     </row>
     <row r="491" spans="1:5">
@@ -8701,13 +8701,13 @@
         <v>3089691.857592373</v>
       </c>
       <c r="C491">
-        <v>3983693.879234985</v>
+        <v>3983725.775164167</v>
       </c>
       <c r="D491">
-        <v>7154514.097889249</v>
+        <v>7156441.312385523</v>
       </c>
       <c r="E491">
-        <v>9555206.639756901</v>
+        <v>9565626.789997913</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -8718,13 +8718,13 @@
         <v>2690162.738076118</v>
       </c>
       <c r="C492">
-        <v>3843563.943784507</v>
+        <v>3843594.717746332</v>
       </c>
       <c r="D492">
-        <v>7485358.680450602</v>
+        <v>7487375.014692368</v>
       </c>
       <c r="E492">
-        <v>11004962.12992691</v>
+        <v>11016963.26848035</v>
       </c>
     </row>
     <row r="493" spans="1:5">
@@ -8735,13 +8735,13 @@
         <v>2690162.738076118</v>
       </c>
       <c r="C493">
-        <v>3843563.943784507</v>
+        <v>3843594.717746332</v>
       </c>
       <c r="D493">
-        <v>7485358.680450602</v>
+        <v>7487375.014692368</v>
       </c>
       <c r="E493">
-        <v>11004962.12992691</v>
+        <v>11016963.26848035</v>
       </c>
     </row>
     <row r="494" spans="1:5">
@@ -8752,13 +8752,13 @@
         <v>2690162.738076118</v>
       </c>
       <c r="C494">
-        <v>3843563.943784507</v>
+        <v>3843594.717746332</v>
       </c>
       <c r="D494">
-        <v>7485358.680450602</v>
+        <v>7487375.014692368</v>
       </c>
       <c r="E494">
-        <v>11004962.12992691</v>
+        <v>11016963.26848035</v>
       </c>
     </row>
     <row r="495" spans="1:5">
@@ -8769,13 +8769,13 @@
         <v>455896.8510348428</v>
       </c>
       <c r="C495">
-        <v>671688.0248986344</v>
+        <v>672113.4707090489</v>
       </c>
       <c r="D495">
-        <v>1354178.15366797</v>
+        <v>1359585.339252583</v>
       </c>
       <c r="E495">
-        <v>1864986.579755214</v>
+        <v>1877293.908429834</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -8786,13 +8786,13 @@
         <v>3395245.809653075</v>
       </c>
       <c r="C496">
-        <v>4679710.545431414</v>
+        <v>4679958.782027024</v>
       </c>
       <c r="D496">
-        <v>8682683.628773259</v>
+        <v>8696523.250950301</v>
       </c>
       <c r="E496">
-        <v>11810907.67706273</v>
+        <v>11861402.54558939</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -8803,13 +8803,13 @@
         <v>455896.8510348428</v>
       </c>
       <c r="C497">
-        <v>671688.0248986344</v>
+        <v>672113.4707090489</v>
       </c>
       <c r="D497">
-        <v>1354178.15366797</v>
+        <v>1359585.339252583</v>
       </c>
       <c r="E497">
-        <v>1864986.579755214</v>
+        <v>1877293.908429834</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -8820,13 +8820,13 @@
         <v>1032465.1628928</v>
       </c>
       <c r="C498">
-        <v>1387651.593361758</v>
+        <v>1387758.534698989</v>
       </c>
       <c r="D498">
-        <v>2486572.589543689</v>
+        <v>2493739.237656436</v>
       </c>
       <c r="E498">
-        <v>3526836.728619037</v>
+        <v>3547337.696779544</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -8837,13 +8837,13 @@
         <v>1216328.822038093</v>
       </c>
       <c r="C499">
-        <v>1469278.157677156</v>
+        <v>1469391.389681283</v>
       </c>
       <c r="D499">
-        <v>2366254.561017381</v>
+        <v>2373074.435834351</v>
       </c>
       <c r="E499">
-        <v>2771086.001057815</v>
+        <v>2787193.904612499</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -8854,13 +8854,13 @@
         <v>1230472.180433885</v>
       </c>
       <c r="C500">
-        <v>1469278.157677156</v>
+        <v>1469391.389681283</v>
       </c>
       <c r="D500">
-        <v>2366254.561017381</v>
+        <v>2373074.435834351</v>
       </c>
       <c r="E500">
-        <v>2708106.773761047</v>
+        <v>2723848.588598578</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -8874,10 +8874,10 @@
         <v>533853.5992580699</v>
       </c>
       <c r="D501">
-        <v>1223244.737352553</v>
+        <v>1223602.079359616</v>
       </c>
       <c r="E501">
-        <v>2222712.57598489</v>
+        <v>2225937.184684169</v>
       </c>
     </row>
   </sheetData>
